--- a/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
+++ b/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,20 +128,21 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -914,36 +915,36 @@
           <t>Receivables incl. related-party</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="21" t="n">
         <v>1685.533</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>12843.804</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="21" t="n">
         <v>16635.123</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="20">
         <f>Assumptions!$C$16</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="20">
         <f>DCF!B22</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="20">
         <f>DCF!C22</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="20">
         <f>DCF!D22</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="20">
         <f>DCF!E22</f>
         <v/>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="20">
         <f>DCF!F22</f>
         <v/>
       </c>
@@ -954,36 +955,36 @@
           <t>Inventories + development WIP</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="21" t="n">
         <v>2246.917</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="21" t="n">
         <v>32047.946</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="21" t="n">
         <v>33409.382</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="20">
         <f>Assumptions!$C$17</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="20">
         <f>DCF!B23</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="20">
         <f>DCF!C23</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="20">
         <f>DCF!D23</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="20">
         <f>DCF!E23</f>
         <v/>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="20">
         <f>DCF!F23</f>
         <v/>
       </c>
@@ -999,33 +1000,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="21" t="n">
         <v>18029.912</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="21" t="n">
         <v>23101.595</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="20">
         <f>Assumptions!$C$18</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="20">
         <f>DCF!B24</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="20">
         <f>DCF!C24</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="20">
         <f>DCF!D24</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="20">
         <f>DCF!E24</f>
         <v/>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="20">
         <f>DCF!F24</f>
         <v/>
       </c>
@@ -1041,35 +1042,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="19">
         <f>C5+C6-C7</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="19">
         <f>D5+D6-D7</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="19">
         <f>E5+E6-E7</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="20">
         <f>DCF!B25</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="20">
         <f>DCF!C25</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="20">
         <f>DCF!D25</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="20">
         <f>DCF!E25</f>
         <v/>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="20">
         <f>DCF!F25</f>
         <v/>
       </c>
@@ -1080,36 +1081,36 @@
           <t>Cash and bank balances</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="21" t="n">
         <v>2259.902</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="21" t="n">
         <v>7009.67</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="21" t="n">
         <v>12641.987</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="20">
         <f>Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="19">
         <f>E9+DCF!B18+'Income Statement'!F11-('Income Statement'!F13-DCF!B10)*Assumptions!$C$48+(Assumptions!$C$51-Assumptions!$C$10)</f>
         <v/>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="19">
         <f>F9+DCF!C18+'Income Statement'!G11-('Income Statement'!G13-DCF!C10)*Assumptions!$C$48+(Assumptions!$D$51-Assumptions!$C$51)</f>
         <v/>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="19">
         <f>G9+DCF!D18+'Income Statement'!H11-('Income Statement'!H13-DCF!D10)*Assumptions!$C$48+(Assumptions!$E$51-Assumptions!$D$51)</f>
         <v/>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="19">
         <f>H9+DCF!E18+'Income Statement'!I11-('Income Statement'!I13-DCF!E10)*Assumptions!$C$48+(Assumptions!$F$51-Assumptions!$E$51)</f>
         <v/>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="19">
         <f>I9+DCF!F18+'Income Statement'!J11-('Income Statement'!J13-DCF!F10)*Assumptions!$C$48+(Assumptions!$G$51-Assumptions!$F$51)</f>
         <v/>
       </c>
@@ -1120,16 +1121,16 @@
           <t>Total assets (audited)</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
+      <c r="B10" s="21" t="n">
         <v>21311.081</v>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="21" t="n">
         <v>75925.281</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="21" t="n">
         <v>87030.985</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="21" t="n">
         <v>91985.92999999999</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -1167,36 +1168,36 @@
           <t>Gross debt incl. related-party loan</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="21" t="n">
         <v>1976.135</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="21" t="n">
         <v>5364.11</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="21" t="n">
         <v>6789.085999999999</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="20">
         <f>Assumptions!$C$10</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="20">
         <f>Assumptions!$C$51</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="20">
         <f>Assumptions!$D$51</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="20">
         <f>Assumptions!$E$51</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="20">
         <f>Assumptions!$F$51</f>
         <v/>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="20">
         <f>Assumptions!$G$51</f>
         <v/>
       </c>
@@ -1207,39 +1208,39 @@
           <t>Net debt (− = net cash)</t>
         </is>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="19">
         <f>B12-B9</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="19">
         <f>C12-C9</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="19">
         <f>D12-D9</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="19">
         <f>E12-E9</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="19">
         <f>F12-F9</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="19">
         <f>G12-G9</f>
         <v/>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="19">
         <f>H12-H9</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="19">
         <f>I12-I9</f>
         <v/>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="19">
         <f>J12-J9</f>
         <v/>
       </c>
@@ -1250,36 +1251,36 @@
           <t>Equity attributable to owners</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="21" t="n">
         <v>13769.094</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="21" t="n">
         <v>49676.408</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="21" t="n">
         <v>53902.504</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="20">
         <f>Assumptions!$C$15</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="19">
         <f>E14+'Income Statement'!F17</f>
         <v/>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="19">
         <f>F14+'Income Statement'!G17</f>
         <v/>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="19">
         <f>G14+'Income Statement'!H17</f>
         <v/>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="19">
         <f>H14+'Income Statement'!I17</f>
         <v/>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="19">
         <f>I14+'Income Statement'!J17</f>
         <v/>
       </c>
@@ -1290,36 +1291,36 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B15" s="19" t="n">
+      <c r="B15" s="21" t="n">
         <v>1149.566</v>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="21" t="n">
         <v>1186.183</v>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="21" t="n">
         <v>847.48</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="20">
         <f>Assumptions!$C$14</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="19">
         <f>E15+'Income Statement'!F16</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="19">
         <f>F15+'Income Statement'!G16</f>
         <v/>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="19">
         <f>G15+'Income Statement'!H16</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="19">
         <f>H15+'Income Statement'!I16</f>
         <v/>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="19">
         <f>I15+'Income Statement'!J16</f>
         <v/>
       </c>
@@ -1330,35 +1331,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="29">
         <f>(B12-B9)/673.3530000000001</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>(C12-C9)/9794.942</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="29">
         <f>(D12-D9)/4895.552000000001</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="29">
         <f>(F12-F9)/DCF!B13</f>
         <v/>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <f>(G12-G9)/DCF!C13</f>
         <v/>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="29">
         <f>(H12-H9)/DCF!D13</f>
         <v/>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="29">
         <f>(I12-I9)/DCF!E13</f>
         <v/>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="29">
         <f>(J12-J9)/DCF!F13</f>
         <v/>
       </c>
@@ -1461,13 +1462,13 @@
           <t>IFRS net cash from operating activities (audited/reviewed)</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="21" t="n">
         <v>3231.447</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>3860.373</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="21" t="n">
         <v>-3921.027</v>
       </c>
     </row>
@@ -1477,18 +1478,18 @@
           <t>Capital expenditure (PP&amp;E + intangibles + IP)</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="21" t="n">
         <v>1247</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="21" t="n">
         <v>1260.566</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="21" t="n">
         <v>312.49</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Model construct (NOT the IFRS measure): links to the DCF waterfall</t>
         </is>
@@ -1500,23 +1501,23 @@
           <t>NOPAT</t>
         </is>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="20">
         <f>DCF!B14</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="20">
         <f>DCF!C14</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="20">
         <f>DCF!D14</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="20">
         <f>DCF!E14</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="20">
         <f>DCF!F14</f>
         <v/>
       </c>
@@ -1527,23 +1528,23 @@
           <t>+ D&amp;A</t>
         </is>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="20">
         <f>DCF!B15</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="20">
         <f>DCF!C15</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="20">
         <f>DCF!D15</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="20">
         <f>DCF!E15</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="20">
         <f>DCF!F15</f>
         <v/>
       </c>
@@ -1554,23 +1555,23 @@
           <t>− Capex</t>
         </is>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="20">
         <f>DCF!B16</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="20">
         <f>DCF!C16</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="20">
         <f>DCF!D16</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="20">
         <f>DCF!E16</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="20">
         <f>DCF!F16</f>
         <v/>
       </c>
@@ -1581,23 +1582,23 @@
           <t>− Δ working capital</t>
         </is>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="20">
         <f>DCF!B17</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="20">
         <f>DCF!C17</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="20">
         <f>DCF!D17</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="20">
         <f>DCF!E17</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="20">
         <f>DCF!F17</f>
         <v/>
       </c>
@@ -1608,29 +1609,29 @@
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="E13" s="34">
+      <c r="E13" s="35">
         <f>DCF!B18</f>
         <v/>
       </c>
-      <c r="F13" s="34">
+      <c r="F13" s="35">
         <f>DCF!C18</f>
         <v/>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="35">
         <f>DCF!D18</f>
         <v/>
       </c>
-      <c r="H13" s="34">
+      <c r="H13" s="35">
         <f>DCF!E18</f>
         <v/>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="35">
         <f>DCF!F18</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="36" t="inlineStr">
         <is>
           <t>Implied H2-2026 IFRS-basis operating recovery required by the model: the H1 actual was −3,921; the model's FY2026 working-capital absorption of 938 implies roughly +5,978 of H2 operating cash flow — stated, not hidden</t>
         </is>
@@ -1745,39 +1746,39 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="20">
         <f>'Income Statement'!B5</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="20">
         <f>'Income Statement'!C5</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <f>'Income Statement'!D5</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="20">
         <f>'Income Statement'!E5</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="20">
         <f>'Income Statement'!F5</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="20">
         <f>'Income Statement'!G5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="20">
         <f>'Income Statement'!H5</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="20">
         <f>'Income Statement'!I5</f>
         <v/>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="20">
         <f>'Income Statement'!J5</f>
         <v/>
       </c>
@@ -1788,15 +1789,15 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="20">
         <f>'Income Statement'!B7</f>
         <v/>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="20">
         <f>'Income Statement'!C7</f>
         <v/>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="20">
         <f>'Income Statement'!D7</f>
         <v/>
       </c>
@@ -1805,23 +1806,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="20">
         <f>'Income Statement'!F7</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="20">
         <f>'Income Statement'!G7</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="20">
         <f>'Income Statement'!H7</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="20">
         <f>'Income Statement'!I7</f>
         <v/>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="20">
         <f>'Income Statement'!J7</f>
         <v/>
       </c>
@@ -1832,15 +1833,15 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B7" s="9">
+      <c r="B7" s="17">
         <f>'Income Statement'!B8</f>
         <v/>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="17">
         <f>'Income Statement'!C8</f>
         <v/>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="17">
         <f>'Income Statement'!D8</f>
         <v/>
       </c>
@@ -1849,23 +1850,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="17">
         <f>'Income Statement'!F8</f>
         <v/>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="17">
         <f>'Income Statement'!G8</f>
         <v/>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="17">
         <f>'Income Statement'!H8</f>
         <v/>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="17">
         <f>'Income Statement'!I8</f>
         <v/>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="17">
         <f>'Income Statement'!J8</f>
         <v/>
       </c>
@@ -1876,39 +1877,39 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="20">
         <f>'Income Statement'!B17</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="20">
         <f>'Income Statement'!C17</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="20">
         <f>'Income Statement'!D17</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="20">
         <f>'Income Statement'!E17</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="20">
         <f>'Income Statement'!F17</f>
         <v/>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="20">
         <f>'Income Statement'!G17</f>
         <v/>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="20">
         <f>'Income Statement'!H17</f>
         <v/>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="20">
         <f>'Income Statement'!I17</f>
         <v/>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="20">
         <f>'Income Statement'!J17</f>
         <v/>
       </c>
@@ -1939,23 +1940,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="20">
         <f>'Cash Flow'!E13</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="20">
         <f>'Cash Flow'!F13</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="20">
         <f>'Cash Flow'!G13</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="20">
         <f>'Cash Flow'!H13</f>
         <v/>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="20">
         <f>'Cash Flow'!I13</f>
         <v/>
       </c>
@@ -1966,39 +1967,39 @@
           <t>Net debt (− = net cash)</t>
         </is>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="20">
         <f>'Balance Sheet'!B13</f>
         <v/>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="20">
         <f>'Balance Sheet'!C13</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="20">
         <f>'Balance Sheet'!D13</f>
         <v/>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="20">
         <f>'Balance Sheet'!E13</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="20">
         <f>'Balance Sheet'!F13</f>
         <v/>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="20">
         <f>'Balance Sheet'!G13</f>
         <v/>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="20">
         <f>'Balance Sheet'!H13</f>
         <v/>
       </c>
-      <c r="I10" s="18">
+      <c r="I10" s="20">
         <f>'Balance Sheet'!I13</f>
         <v/>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="20">
         <f>'Balance Sheet'!J13</f>
         <v/>
       </c>
@@ -2009,39 +2010,39 @@
           <t>Equity attributable</t>
         </is>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="20">
         <f>'Balance Sheet'!B14</f>
         <v/>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="20">
         <f>'Balance Sheet'!C14</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="20">
         <f>'Balance Sheet'!D14</f>
         <v/>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="20">
         <f>'Balance Sheet'!E14</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="20">
         <f>'Balance Sheet'!F14</f>
         <v/>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="20">
         <f>'Balance Sheet'!G14</f>
         <v/>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="20">
         <f>'Balance Sheet'!H14</f>
         <v/>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="20">
         <f>'Balance Sheet'!I14</f>
         <v/>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="20">
         <f>'Balance Sheet'!J14</f>
         <v/>
       </c>
@@ -2055,27 +2056,27 @@
           <t>Invested capital: 30-Jun-2026 base + cumulative (capex − D&amp;A + ΔWC)</t>
         </is>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="19">
         <f>Assumptions!$C$15+Assumptions!$C$14+Assumptions!$C$10-Assumptions!$C$9</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="19">
         <f>E13+DCF!B16*-1-DCF!B12+DCF!B26</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="19">
         <f>F13+DCF!C16*-1-DCF!C12+DCF!C26</f>
         <v/>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="19">
         <f>G13+DCF!D16*-1-DCF!D12+DCF!D26</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="19">
         <f>H13+DCF!E16*-1-DCF!E12+DCF!E26</f>
         <v/>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="19">
         <f>I13+DCF!F16*-1-DCF!F12+DCF!F26</f>
         <v/>
       </c>
@@ -2142,10 +2143,10 @@
           <t>Sessions in window</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>63</v>
       </c>
     </row>
@@ -2155,12 +2156,12 @@
           <t>Grade date</t>
         </is>
       </c>
-      <c r="B6" s="36" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>2026-11-09</t>
         </is>
@@ -2172,10 +2173,10 @@
           <t>Annualised anchor volatility</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="25" t="n">
         <v>0.2516632167115939</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="25" t="n">
         <v>0.2637248510898824</v>
       </c>
     </row>
@@ -2250,10 +2251,10 @@
           <t>P(close above spot)</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <v>0.51874</v>
       </c>
-      <c r="C13" s="24" t="n">
+      <c r="C13" s="25" t="n">
         <v>0.53302</v>
       </c>
     </row>
@@ -2263,10 +2264,10 @@
           <t>P(≥ +10%)</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="25" t="n">
         <v>0.08014</v>
       </c>
-      <c r="C14" s="24" t="n">
+      <c r="C14" s="25" t="n">
         <v>0.23496</v>
       </c>
     </row>
@@ -2276,10 +2277,10 @@
           <t>P(≤ −10%)</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="25" t="n">
         <v>0.05528</v>
       </c>
-      <c r="C15" s="24" t="n">
+      <c r="C15" s="25" t="n">
         <v>0.16866</v>
       </c>
     </row>
@@ -2289,10 +2290,10 @@
           <t>P(touch +5% at any point)</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="25" t="n">
         <v>0.3935</v>
       </c>
-      <c r="C16" s="24" t="n">
+      <c r="C16" s="25" t="n">
         <v>0.6544</v>
       </c>
     </row>
@@ -2302,15 +2303,15 @@
           <t>P(touch −5% at any point)</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="25" t="n">
         <v>0.34584</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="25" t="n">
         <v>0.589</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="22" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Calibration evidence (walk-forward, this name)</t>
         </is>
@@ -2322,7 +2323,7 @@
           <t>Windows scored (post-break)</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n">
+      <c r="B20" s="21" t="n">
         <v>17</v>
       </c>
     </row>
@@ -2332,7 +2333,7 @@
           <t>CRPS skill vs carry-anchored random walk</t>
         </is>
       </c>
-      <c r="B21" s="21" t="n">
+      <c r="B21" s="23" t="n">
         <v>0.04239890936861235</v>
       </c>
     </row>
@@ -2342,7 +2343,7 @@
           <t>Verdict</t>
         </is>
       </c>
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -2354,7 +2355,7 @@
           <t>Coverage of the 80% band (over-covered: bands run wide)</t>
         </is>
       </c>
-      <c r="B23" s="24" t="n">
+      <c r="B23" s="25" t="n">
         <v>0.9411764705882353</v>
       </c>
     </row>
@@ -2364,7 +2365,7 @@
           <t>Coverage of the 90% band</t>
         </is>
       </c>
-      <c r="B24" s="24" t="n">
+      <c r="B24" s="25" t="n">
         <v>0.9411764705882353</v>
       </c>
     </row>
@@ -2374,7 +2375,7 @@
           <t>PIT mean (0.5 = centred)</t>
         </is>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="38" t="n">
         <v>0.439185294117647</v>
       </c>
     </row>
@@ -3130,35 +3131,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="17">
         <f>'Income Statement'!C17/1.0/(('Balance Sheet'!C14+'Balance Sheet'!B14)/2)</f>
         <v/>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="17">
         <f>'Income Statement'!D17/1.0/(('Balance Sheet'!D14+'Balance Sheet'!C14)/2)</f>
         <v/>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="17">
         <f>'Income Statement'!E17/0.5/(('Balance Sheet'!E14+'Balance Sheet'!D14)/2)</f>
         <v/>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="17">
         <f>'Income Statement'!F17/0.5/(('Balance Sheet'!F14+'Balance Sheet'!E14)/2)</f>
         <v/>
       </c>
-      <c r="G7" s="9">
+      <c r="G7" s="17">
         <f>'Income Statement'!G17/1.0/(('Balance Sheet'!G14+'Balance Sheet'!F14)/2)</f>
         <v/>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="17">
         <f>'Income Statement'!H17/1.0/(('Balance Sheet'!H14+'Balance Sheet'!G14)/2)</f>
         <v/>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="17">
         <f>'Income Statement'!I17/1.0/(('Balance Sheet'!I14+'Balance Sheet'!H14)/2)</f>
         <v/>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="17">
         <f>'Income Statement'!J17/1.0/(('Balance Sheet'!J14+'Balance Sheet'!I14)/2)</f>
         <v/>
       </c>
@@ -3189,23 +3190,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="17">
         <f>DCF!B14/0.5/(('Summary Financials'!F13+'Summary Financials'!E13)/2)</f>
         <v/>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="17">
         <f>DCF!C14/1.0/(('Summary Financials'!G13+'Summary Financials'!F13)/2)</f>
         <v/>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="17">
         <f>DCF!D14/1.0/(('Summary Financials'!H13+'Summary Financials'!G13)/2)</f>
         <v/>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="17">
         <f>DCF!E14/1.0/(('Summary Financials'!I13+'Summary Financials'!H13)/2)</f>
         <v/>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="17">
         <f>DCF!F14/1.0/(('Summary Financials'!J13+'Summary Financials'!I13)/2)</f>
         <v/>
       </c>
@@ -3216,15 +3217,15 @@
           <t>P/E at spot (full years)</t>
         </is>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="29">
         <f>Assumptions!$C$4/B5</f>
         <v/>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <f>Assumptions!$C$4/C5</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <f>Assumptions!$C$4/D5</f>
         <v/>
       </c>
@@ -3238,19 +3239,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <f>Assumptions!$C$4/G5</f>
         <v/>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="29">
         <f>Assumptions!$C$4/H5</f>
         <v/>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="29">
         <f>Assumptions!$C$4/I5</f>
         <v/>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="29">
         <f>Assumptions!$C$4/J5</f>
         <v/>
       </c>
@@ -3261,39 +3262,39 @@
           <t>P/B at spot</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>Assumptions!$C$4/B6</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>Assumptions!$C$4/C6</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>Assumptions!$C$4/D6</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>Assumptions!$C$4/E6</f>
         <v/>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>Assumptions!$C$4/F6</f>
         <v/>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <f>Assumptions!$C$4/G6</f>
         <v/>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <f>Assumptions!$C$4/H6</f>
         <v/>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <f>Assumptions!$C$4/I6</f>
         <v/>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="29">
         <f>Assumptions!$C$4/J6</f>
         <v/>
       </c>
@@ -3389,21 +3390,21 @@
       <c r="B5" s="7" t="n">
         <v>7.78</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>7862.6</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="19">
         <f>B5*C5</f>
         <v/>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="21" t="n">
         <v>7548</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>D5/E5</f>
         <v/>
       </c>
-      <c r="G5" s="19" t="n">
+      <c r="G5" s="21" t="n">
         <v>71700</v>
       </c>
     </row>
@@ -3416,21 +3417,21 @@
       <c r="B6" s="7" t="n">
         <v>11.5</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="21" t="n">
         <v>8838</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="19">
         <f>B6*C6</f>
         <v/>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="21" t="n">
         <v>17599</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="29">
         <f>D6/E6</f>
         <v/>
       </c>
-      <c r="G6" s="19" t="n">
+      <c r="G6" s="21" t="n">
         <v>155000</v>
       </c>
     </row>
@@ -3443,26 +3444,26 @@
       <c r="B7" s="7" t="n">
         <v>13.38</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="21" t="n">
         <v>4000</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="19">
         <f>B7*C7</f>
         <v/>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="21" t="n">
         <v>11316</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="29">
         <f>D7/E7</f>
         <v/>
       </c>
-      <c r="G7" s="19" t="n">
+      <c r="G7" s="21" t="n">
         <v>125200</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Modon Holding (this study)</t>
         </is>
@@ -3471,23 +3472,23 @@
         <f>Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="20">
         <f>Assumptions!$C$5</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="19">
         <f>B8*C8</f>
         <v/>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="20">
         <f>Assumptions!$C$71</f>
         <v/>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>D8/E8</f>
         <v/>
       </c>
-      <c r="G8" s="19" t="n">
+      <c r="G8" s="21" t="n">
         <v>65400</v>
       </c>
     </row>
@@ -3499,7 +3500,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="36" t="inlineStr">
         <is>
           <t>Sector context (ADREC 2025, regulator): AED 142bn transactions (+44%); residential AED 76bn (+67%); off-plan 71% of residential deals; expatriate and foreign buyers 62% of residential sales value.</t>
         </is>
@@ -3521,7 +3522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3606,16 +3607,13 @@
       <c r="D5" s="7" t="n">
         <v>4.13375247645742</v>
       </c>
-      <c r="E5" s="9">
-        <f>Assumptions!$C$82</f>
-        <v/>
-      </c>
-      <c r="F5" s="10">
-        <f>C5*E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>C5/$C$14-1</f>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the class primary</t>
+        </is>
+      </c>
+      <c r="G5" s="9">
+        <f>C5/$C$15-1</f>
         <v/>
       </c>
     </row>
@@ -3637,16 +3635,13 @@
         <f>'Relative &amp; Normalized'!D12</f>
         <v/>
       </c>
-      <c r="E6" s="9">
-        <f>Assumptions!$C$83</f>
-        <v/>
-      </c>
-      <c r="F6" s="10">
-        <f>C6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
-        <f>C6/$C$14-1</f>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>cross-check</t>
+        </is>
+      </c>
+      <c r="G6" s="9">
+        <f>C6/$C$15-1</f>
         <v/>
       </c>
     </row>
@@ -3668,16 +3663,13 @@
         <f>'Relative &amp; Normalized'!F28</f>
         <v/>
       </c>
-      <c r="E7" s="9">
-        <f>Assumptions!$C$84</f>
-        <v/>
-      </c>
-      <c r="F7" s="10">
-        <f>C7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
-        <f>C7/$C$14-1</f>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>REMOVED — not a lens this class publishes</t>
+        </is>
+      </c>
+      <c r="G7" s="9">
+        <f>C7/$C$15-1</f>
         <v/>
       </c>
     </row>
@@ -3699,276 +3691,294 @@
         <f>'Relative &amp; Normalized'!F36</f>
         <v/>
       </c>
-      <c r="E8" s="9">
-        <f>Assumptions!$C$85</f>
-        <v/>
-      </c>
-      <c r="F8" s="10">
-        <f>C8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
-        <f>C8/$C$14-1</f>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>a disclosed floor, never weighted</t>
+        </is>
+      </c>
+      <c r="G8" s="9">
+        <f>C8/$C$15-1</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Weighted central</t>
-        </is>
-      </c>
-      <c r="B9" s="13">
-        <f>MIN(B5:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>SUM(F5:F8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="13">
-        <f>MAX(D5:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>SUM(E5:E8)</f>
-        <v/>
-      </c>
-      <c r="F9" s="15" t="n"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>THE CENTRAL — the cash-flow lens, not an average</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>the class primary</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n"/>
       <c r="G9" s="14">
-        <f>C9/$C$14-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>The contested judgement: DCF base vs run-off stress</t>
-        </is>
-      </c>
-      <c r="C11" s="8">
-        <f>DCF!C62</f>
-        <v/>
-      </c>
-      <c r="D11" s="7" t="n">
-        <v>2.643232316556594</v>
+        <f>C9/$C$15-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>NOT AVERAGED — the retired blend, published unused</t>
+        </is>
+      </c>
+      <c r="C10" s="16">
+        <f>C5*0.4+C6*0.2+C7*0.2+C8*0.2</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>retired 02-Sep-2026</t>
+        </is>
+      </c>
+      <c r="G10" s="9">
+        <f>C10/$C$15-1</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Terminal value share of DCF enterprise value</t>
-        </is>
-      </c>
-      <c r="C12" s="9">
-        <f>DCF!C49</f>
-        <v/>
+          <t>The contested judgement: DCF base vs run-off stress</t>
+        </is>
+      </c>
+      <c r="C12" s="8">
+        <f>DCF!C62</f>
+        <v/>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2.643232316556594</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>Terminal value share of DCF enterprise value</t>
+        </is>
+      </c>
+      <c r="C13" s="17">
+        <f>DCF!C49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>Expert panel median</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C14" s="7" t="n">
         <v>2.478745616179524</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Market price (anchor, 7-Aug-2026)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="16">
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="18">
         <f>Assumptions!$C$4</f>
         <v/>
       </c>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-      <c r="G14" s="15" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="D15" s="13" t="n"/>
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="13" t="n"/>
+      <c r="G15" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Key figure</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Market capitalisation (AED mn)</t>
-        </is>
-      </c>
-      <c r="C17" s="17">
-        <f>Assumptions!$C$4*Assumptions!$C$5</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Net cash, strict basis (all cash − all debt, 30-Jun-2026)</t>
-        </is>
-      </c>
-      <c r="C18" s="18">
-        <f>Assumptions!$C$9-Assumptions!$C$10</f>
+          <t>Market capitalisation (AED mn)</t>
+        </is>
+      </c>
+      <c r="C18" s="19">
+        <f>Assumptions!$C$4*Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Net debt, company definition (available cash − debt, disclosed)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>-912</v>
+          <t>Net cash, strict basis (all cash − all debt, 30-Jun-2026)</t>
+        </is>
+      </c>
+      <c r="C19" s="20">
+        <f>Assumptions!$C$9-Assumptions!$C$10</f>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>FY2026E revenue (H1 actual + H2 model)</t>
-        </is>
-      </c>
-      <c r="C20" s="18">
-        <f>Assumptions!$C$19+DCF!B5</f>
-        <v/>
+          <t>Net debt, company definition (available cash − debt, disclosed)</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>-912</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>FY2026E attributable profit</t>
-        </is>
-      </c>
-      <c r="C21" s="18">
-        <f>'Relative &amp; Normalized'!C5</f>
+          <t>FY2026E revenue (H1 actual + H2 model)</t>
+        </is>
+      </c>
+      <c r="C21" s="20">
+        <f>Assumptions!$C$19+DCF!B5</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital (explicit window)</t>
+          <t>FY2026E attributable profit</t>
         </is>
       </c>
       <c r="C22" s="20">
-        <f>DCF!C36</f>
+        <f>'Relative &amp; Normalized'!C5</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Cost of capital (terminal, derived weights)</t>
-        </is>
-      </c>
-      <c r="C23" s="20">
-        <f>DCF!C38</f>
+          <t>Cost of capital (explicit window)</t>
+        </is>
+      </c>
+      <c r="C23" s="22">
+        <f>DCF!C36</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
+          <t>Cost of capital (terminal, derived weights)</t>
+        </is>
+      </c>
+      <c r="C24" s="22">
+        <f>DCF!C38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C24" s="20">
+      <c r="C25" s="22">
         <f>Assumptions!$C$66</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Monte Carlo price map (engine re-run, pasted)</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>1 month</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>3 months</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>5th percentile</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n">
-        <v>2.537067974301798</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>2.319965747344324</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>25th percentile</t>
+          <t>5th percentile</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>2.718595960543321</v>
+        <v>2.537067974301798</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>2.637975726186433</v>
+        <v>2.319965747344324</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Median</t>
+          <t>25th percentile</t>
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>2.838308856303401</v>
+        <v>2.718595960543321</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>2.857647930306376</v>
+        <v>2.637975726186433</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>75th percentile</t>
+          <t>Median</t>
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>2.963942198127806</v>
+        <v>2.838308856303401</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>3.094773382373537</v>
+        <v>2.857647930306376</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
+          <t>75th percentile</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n">
+        <v>2.963942198127806</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <v>3.094773382373537</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
           <t>95th percentile</t>
         </is>
       </c>
-      <c r="B31" s="7" t="n">
+      <c r="B32" s="7" t="n">
         <v>3.169632883184554</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C32" s="7" t="n">
         <v>3.523723381103312</v>
       </c>
     </row>
@@ -4148,13 +4158,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Weighted central (links to Summary)</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="13">
+      <c r="B14" s="13" t="n"/>
+      <c r="C14" s="11">
         <f>Summary!C9</f>
         <v/>
       </c>
@@ -4170,7 +4180,7 @@
           <t>cost-of-equity adder reconciling the base DCF to spot (engine solve)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="23" t="n">
         <v>0.02693414991240069</v>
       </c>
     </row>
@@ -4237,12 +4247,12 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Panel median</t>
         </is>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="24">
         <f>MEDIAN(C19:C21)</f>
         <v/>
       </c>
@@ -4258,7 +4268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -4341,23 +4351,23 @@
           <t>Shares outstanding (mn)</t>
         </is>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>16347.08</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>30-Jun-2026 anchors (reviewed interim + results release, pasted)</t>
         </is>
       </c>
-      <c r="B6" s="15" t="n"/>
-      <c r="C6" s="15" t="n"/>
-      <c r="D6" s="15" t="n"/>
-      <c r="E6" s="15" t="n"/>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
-      <c r="H6" s="15" t="n"/>
+      <c r="B6" s="13" t="n"/>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="13" t="n"/>
+      <c r="F6" s="13" t="n"/>
+      <c r="G6" s="13" t="n"/>
+      <c r="H6" s="13" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -4365,7 +4375,7 @@
           <t>Development backlog at 30-Jun-2026 (65.4bn × 95%, disclosed)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="21" t="n">
         <v>62130</v>
       </c>
     </row>
@@ -4375,7 +4385,7 @@
           <t>Unrestricted (available) cash at 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="21" t="n">
         <v>8600</v>
       </c>
     </row>
@@ -4385,7 +4395,7 @@
           <t>Total cash and bank balances at 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="21" t="n">
         <v>12303.24</v>
       </c>
     </row>
@@ -4395,7 +4405,7 @@
           <t>Gross debt incl. related-party loan at 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="21" t="n">
         <v>9541.684999999999</v>
       </c>
     </row>
@@ -4405,7 +4415,7 @@
           <t>Lease liabilities at 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="21" t="n">
         <v>644.799</v>
       </c>
     </row>
@@ -4415,7 +4425,7 @@
           <t>Associates &amp; JVs at carrying value, 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="21" t="n">
         <v>2826.454</v>
       </c>
     </row>
@@ -4425,7 +4435,7 @@
           <t>Investments in financial assets, 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="21" t="n">
         <v>392.972</v>
       </c>
     </row>
@@ -4435,7 +4445,7 @@
           <t>Non-controlling interests, 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="21" t="n">
         <v>922.342</v>
       </c>
     </row>
@@ -4445,7 +4455,7 @@
           <t>Equity attributable to owners, 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="n">
+      <c r="C15" s="21" t="n">
         <v>56396.629</v>
       </c>
     </row>
@@ -4455,7 +4465,7 @@
           <t>Receivables incl. related-party, 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="21" t="n">
         <v>22155.68</v>
       </c>
     </row>
@@ -4465,7 +4475,7 @@
           <t>Inventories + development WIP, 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C17" s="19" t="n">
+      <c r="C17" s="21" t="n">
         <v>34087.289</v>
       </c>
     </row>
@@ -4475,7 +4485,7 @@
           <t>Payables incl. advances + related-party, 30-Jun-2026 (disclosed)</t>
         </is>
       </c>
-      <c r="C18" s="19" t="n">
+      <c r="C18" s="21" t="n">
         <v>22289.32</v>
       </c>
     </row>
@@ -4485,7 +4495,7 @@
           <t>H1-2026 revenue (actual)</t>
         </is>
       </c>
-      <c r="C19" s="19" t="n">
+      <c r="C19" s="21" t="n">
         <v>9188.304</v>
       </c>
     </row>
@@ -4495,7 +4505,7 @@
           <t>H1-2026 gross profit (actual)</t>
         </is>
       </c>
-      <c r="C20" s="19" t="n">
+      <c r="C20" s="21" t="n">
         <v>3201.275</v>
       </c>
     </row>
@@ -4505,7 +4515,7 @@
           <t>H1-2026 attributable profit (actual)</t>
         </is>
       </c>
-      <c r="C21" s="19" t="n">
+      <c r="C21" s="21" t="n">
         <v>2162.966</v>
       </c>
     </row>
@@ -4515,7 +4525,7 @@
           <t>H1-2026 adjusted EBITDA (disclosed)</t>
         </is>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="21" t="n">
         <v>2995</v>
       </c>
     </row>
@@ -4525,23 +4535,23 @@
           <t>Depreciable asset base at 30-Jun-2026 (PP&amp;E+IP+ROU+intangibles)</t>
         </is>
       </c>
-      <c r="C23" s="19" t="n">
+      <c r="C23" s="21" t="n">
         <v>19736.134</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Forecast drivers (H2-2026 stub, then annual)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="15" t="n"/>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="13" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
+      <c r="G24" s="13" t="n"/>
+      <c r="H24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -4549,19 +4559,19 @@
           <t>Backlog conversion rate on opening development backlog</t>
         </is>
       </c>
-      <c r="C25" s="24" t="n">
+      <c r="C25" s="25" t="n">
         <v>0.105</v>
       </c>
-      <c r="D25" s="24" t="n">
+      <c r="D25" s="25" t="n">
         <v>0.25</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="25" t="n">
         <v>0.28</v>
       </c>
-      <c r="F25" s="24" t="n">
+      <c r="F25" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="G25" s="24" t="n">
+      <c r="G25" s="25" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -4571,19 +4581,19 @@
           <t>New development sales (AED mn)</t>
         </is>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="21" t="n">
         <v>12000</v>
       </c>
-      <c r="D26" s="19" t="n">
+      <c r="D26" s="21" t="n">
         <v>30000</v>
       </c>
-      <c r="E26" s="19" t="n">
+      <c r="E26" s="21" t="n">
         <v>26000</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="21" t="n">
         <v>23000</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G26" s="21" t="n">
         <v>21000</v>
       </c>
     </row>
@@ -4593,19 +4603,19 @@
           <t>Land and plot sales revenue (AED mn)</t>
         </is>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="21" t="n">
         <v>700</v>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="21" t="n">
         <v>1400</v>
       </c>
-      <c r="E27" s="19" t="n">
+      <c r="E27" s="21" t="n">
         <v>1300</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="21" t="n">
         <v>1200</v>
       </c>
-      <c r="G27" s="19" t="n">
+      <c r="G27" s="21" t="n">
         <v>1100</v>
       </c>
     </row>
@@ -4615,19 +4625,19 @@
           <t>Development gross margin</t>
         </is>
       </c>
-      <c r="C28" s="24" t="n">
+      <c r="C28" s="25" t="n">
         <v>0.41</v>
       </c>
-      <c r="D28" s="24" t="n">
+      <c r="D28" s="25" t="n">
         <v>0.4</v>
       </c>
-      <c r="E28" s="24" t="n">
+      <c r="E28" s="25" t="n">
         <v>0.39</v>
       </c>
-      <c r="F28" s="24" t="n">
+      <c r="F28" s="25" t="n">
         <v>0.385</v>
       </c>
-      <c r="G28" s="24" t="n">
+      <c r="G28" s="25" t="n">
         <v>0.38</v>
       </c>
     </row>
@@ -4637,19 +4647,19 @@
           <t>Asset &amp; investment management growth (from FY27)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="n">
+      <c r="C29" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D29" s="24" t="n">
+      <c r="D29" s="25" t="n">
         <v>0.09</v>
       </c>
-      <c r="E29" s="24" t="n">
+      <c r="E29" s="25" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F29" s="25" t="n">
         <v>0.08</v>
       </c>
-      <c r="G29" s="24" t="n">
+      <c r="G29" s="25" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -4659,7 +4669,7 @@
           <t>Asset &amp; investment management H2-2026E revenue</t>
         </is>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="21" t="n">
         <v>385</v>
       </c>
     </row>
@@ -4669,19 +4679,19 @@
           <t>Asset &amp; investment management gross margin</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n">
+      <c r="C31" s="25" t="n">
         <v>0.68</v>
       </c>
-      <c r="D31" s="24" t="n">
+      <c r="D31" s="25" t="n">
         <v>0.66</v>
       </c>
-      <c r="E31" s="24" t="n">
+      <c r="E31" s="25" t="n">
         <v>0.65</v>
       </c>
-      <c r="F31" s="24" t="n">
+      <c r="F31" s="25" t="n">
         <v>0.64</v>
       </c>
-      <c r="G31" s="24" t="n">
+      <c r="G31" s="25" t="n">
         <v>0.64</v>
       </c>
     </row>
@@ -4691,19 +4701,19 @@
           <t>Hospitality growth (from FY27)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n">
+      <c r="C32" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D32" s="24" t="n">
+      <c r="D32" s="25" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E32" s="24" t="n">
+      <c r="E32" s="25" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="25" t="n">
         <v>0.06</v>
       </c>
-      <c r="G32" s="24" t="n">
+      <c r="G32" s="25" t="n">
         <v>0.06</v>
       </c>
     </row>
@@ -4713,7 +4723,7 @@
           <t>Hospitality H2-2026E revenue</t>
         </is>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C33" s="21" t="n">
         <v>452</v>
       </c>
     </row>
@@ -4723,19 +4733,19 @@
           <t>Hospitality gross margin</t>
         </is>
       </c>
-      <c r="C34" s="24" t="n">
+      <c r="C34" s="25" t="n">
         <v>0.29</v>
       </c>
-      <c r="D34" s="24" t="n">
+      <c r="D34" s="25" t="n">
         <v>0.28</v>
       </c>
-      <c r="E34" s="24" t="n">
+      <c r="E34" s="25" t="n">
         <v>0.29</v>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="25" t="n">
         <v>0.3</v>
       </c>
-      <c r="G34" s="24" t="n">
+      <c r="G34" s="25" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -4745,19 +4755,19 @@
           <t>Events, catering &amp; tourism growth (from FY27)</t>
         </is>
       </c>
-      <c r="C35" s="24" t="n">
+      <c r="C35" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="24" t="n">
+      <c r="D35" s="25" t="n">
         <v>0.045</v>
       </c>
-      <c r="E35" s="24" t="n">
+      <c r="E35" s="25" t="n">
         <v>0.043</v>
       </c>
-      <c r="F35" s="24" t="n">
+      <c r="F35" s="25" t="n">
         <v>0.041</v>
       </c>
-      <c r="G35" s="24" t="n">
+      <c r="G35" s="25" t="n">
         <v>0.039</v>
       </c>
     </row>
@@ -4767,7 +4777,7 @@
           <t>Events, catering &amp; tourism H2-2026E revenue</t>
         </is>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="21" t="n">
         <v>3000</v>
       </c>
     </row>
@@ -4777,19 +4787,19 @@
           <t>Events, catering &amp; tourism gross margin</t>
         </is>
       </c>
-      <c r="C37" s="24" t="n">
+      <c r="C37" s="25" t="n">
         <v>0.29</v>
       </c>
-      <c r="D37" s="24" t="n">
+      <c r="D37" s="25" t="n">
         <v>0.27</v>
       </c>
-      <c r="E37" s="24" t="n">
+      <c r="E37" s="25" t="n">
         <v>0.275</v>
       </c>
-      <c r="F37" s="24" t="n">
+      <c r="F37" s="25" t="n">
         <v>0.28</v>
       </c>
-      <c r="G37" s="24" t="n">
+      <c r="G37" s="25" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -4799,7 +4809,7 @@
           <t>H1-2026 AIM revenue (actual)</t>
         </is>
       </c>
-      <c r="C38" s="19" t="n">
+      <c r="C38" s="21" t="n">
         <v>360.966</v>
       </c>
     </row>
@@ -4809,7 +4819,7 @@
           <t>H1-2026 Hospitality revenue (actual)</t>
         </is>
       </c>
-      <c r="C39" s="19" t="n">
+      <c r="C39" s="21" t="n">
         <v>388.398</v>
       </c>
     </row>
@@ -4819,7 +4829,7 @@
           <t>H1-2026 ECT revenue (actual)</t>
         </is>
       </c>
-      <c r="C40" s="19" t="n">
+      <c r="C40" s="21" t="n">
         <v>2775.402</v>
       </c>
     </row>
@@ -4829,7 +4839,7 @@
           <t>Others / eliminations revenue (full-year rate)</t>
         </is>
       </c>
-      <c r="C41" s="19" t="n">
+      <c r="C41" s="21" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -4839,7 +4849,7 @@
           <t>Others gross loss (full-year rate)</t>
         </is>
       </c>
-      <c r="C42" s="19" t="n">
+      <c r="C42" s="21" t="n">
         <v>-120</v>
       </c>
     </row>
@@ -4849,19 +4859,19 @@
           <t>General &amp; administrative / revenue</t>
         </is>
       </c>
-      <c r="C43" s="24" t="n">
+      <c r="C43" s="25" t="n">
         <v>0.083</v>
       </c>
-      <c r="D43" s="24" t="n">
+      <c r="D43" s="25" t="n">
         <v>0.08799999999999999</v>
       </c>
-      <c r="E43" s="24" t="n">
+      <c r="E43" s="25" t="n">
         <v>0.08699999999999999</v>
       </c>
-      <c r="F43" s="24" t="n">
+      <c r="F43" s="25" t="n">
         <v>0.08599999999999999</v>
       </c>
-      <c r="G43" s="24" t="n">
+      <c r="G43" s="25" t="n">
         <v>0.08500000000000001</v>
       </c>
     </row>
@@ -4871,19 +4881,19 @@
           <t>Selling &amp; marketing / revenue</t>
         </is>
       </c>
-      <c r="C44" s="24" t="n">
+      <c r="C44" s="25" t="n">
         <v>0.017</v>
       </c>
-      <c r="D44" s="24" t="n">
+      <c r="D44" s="25" t="n">
         <v>0.018</v>
       </c>
-      <c r="E44" s="24" t="n">
+      <c r="E44" s="25" t="n">
         <v>0.017</v>
       </c>
-      <c r="F44" s="24" t="n">
+      <c r="F44" s="25" t="n">
         <v>0.017</v>
       </c>
-      <c r="G44" s="24" t="n">
+      <c r="G44" s="25" t="n">
         <v>0.016</v>
       </c>
     </row>
@@ -4893,19 +4903,19 @@
           <t>Investment and other income, recurring (AED mn)</t>
         </is>
       </c>
-      <c r="C45" s="19" t="n">
+      <c r="C45" s="21" t="n">
         <v>80</v>
       </c>
-      <c r="D45" s="19" t="n">
+      <c r="D45" s="21" t="n">
         <v>165</v>
       </c>
-      <c r="E45" s="19" t="n">
+      <c r="E45" s="21" t="n">
         <v>170</v>
       </c>
-      <c r="F45" s="19" t="n">
+      <c r="F45" s="21" t="n">
         <v>175</v>
       </c>
-      <c r="G45" s="19" t="n">
+      <c r="G45" s="21" t="n">
         <v>180</v>
       </c>
     </row>
@@ -4915,7 +4925,7 @@
           <t>D&amp;A rate on the average depreciable asset base</t>
         </is>
       </c>
-      <c r="C46" s="21" t="n">
+      <c r="C46" s="23" t="n">
         <v>0.034</v>
       </c>
     </row>
@@ -4925,19 +4935,19 @@
           <t>Capital expenditure (AED mn)</t>
         </is>
       </c>
-      <c r="C47" s="19" t="n">
+      <c r="C47" s="21" t="n">
         <v>700</v>
       </c>
-      <c r="D47" s="19" t="n">
+      <c r="D47" s="21" t="n">
         <v>1500</v>
       </c>
-      <c r="E47" s="19" t="n">
+      <c r="E47" s="21" t="n">
         <v>1550</v>
       </c>
-      <c r="F47" s="19" t="n">
+      <c r="F47" s="21" t="n">
         <v>1600</v>
       </c>
-      <c r="G47" s="19" t="n">
+      <c r="G47" s="21" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -4947,7 +4957,7 @@
           <t>Effective tax rate (DMTT floor + foreign uplift)</t>
         </is>
       </c>
-      <c r="C48" s="24" t="n">
+      <c r="C48" s="25" t="n">
         <v>0.155</v>
       </c>
     </row>
@@ -4957,7 +4967,7 @@
           <t>NCI share of profit</t>
         </is>
       </c>
-      <c r="C49" s="24" t="n">
+      <c r="C49" s="25" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -4967,19 +4977,19 @@
           <t>Associate income path (AED mn)</t>
         </is>
       </c>
-      <c r="C50" s="19" t="n">
+      <c r="C50" s="21" t="n">
         <v>95</v>
       </c>
-      <c r="D50" s="19" t="n">
+      <c r="D50" s="21" t="n">
         <v>210</v>
       </c>
-      <c r="E50" s="19" t="n">
+      <c r="E50" s="21" t="n">
         <v>227</v>
       </c>
-      <c r="F50" s="19" t="n">
+      <c r="F50" s="21" t="n">
         <v>245</v>
       </c>
-      <c r="G50" s="19" t="n">
+      <c r="G50" s="21" t="n">
         <v>264</v>
       </c>
     </row>
@@ -4989,19 +4999,19 @@
           <t>Gross debt path incl. related-party loan (AED mn)</t>
         </is>
       </c>
-      <c r="C51" s="19" t="n">
+      <c r="C51" s="21" t="n">
         <v>10300</v>
       </c>
-      <c r="D51" s="19" t="n">
+      <c r="D51" s="21" t="n">
         <v>10500</v>
       </c>
-      <c r="E51" s="19" t="n">
+      <c r="E51" s="21" t="n">
         <v>9700</v>
       </c>
-      <c r="F51" s="19" t="n">
+      <c r="F51" s="21" t="n">
         <v>8800</v>
       </c>
-      <c r="G51" s="19" t="n">
+      <c r="G51" s="21" t="n">
         <v>7900</v>
       </c>
     </row>
@@ -5011,7 +5021,7 @@
           <t>Yield on cash balances</t>
         </is>
       </c>
-      <c r="C52" s="24" t="n">
+      <c r="C52" s="25" t="n">
         <v>0.035</v>
       </c>
     </row>
@@ -5021,23 +5031,23 @@
           <t>Interest on lease liabilities (AED mn/yr)</t>
         </is>
       </c>
-      <c r="C53" s="19" t="n">
+      <c r="C53" s="21" t="n">
         <v>36</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="12" t="inlineStr">
+      <c r="A54" s="10" t="inlineStr">
         <is>
           <t>Working capital components (calibrated 31-Dec-25 and 30-Jun-26)</t>
         </is>
       </c>
-      <c r="B54" s="15" t="n"/>
-      <c r="C54" s="15" t="n"/>
-      <c r="D54" s="15" t="n"/>
-      <c r="E54" s="15" t="n"/>
-      <c r="F54" s="15" t="n"/>
-      <c r="G54" s="15" t="n"/>
-      <c r="H54" s="15" t="n"/>
+      <c r="B54" s="13" t="n"/>
+      <c r="C54" s="13" t="n"/>
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="13" t="n"/>
+      <c r="G54" s="13" t="n"/>
+      <c r="H54" s="13" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -5045,19 +5055,19 @@
           <t>Receivable days (incl. related-party) on revenue</t>
         </is>
       </c>
-      <c r="C55" s="19" t="n">
+      <c r="C55" s="21" t="n">
         <v>440</v>
       </c>
-      <c r="D55" s="19" t="n">
+      <c r="D55" s="21" t="n">
         <v>430</v>
       </c>
-      <c r="E55" s="19" t="n">
+      <c r="E55" s="21" t="n">
         <v>410</v>
       </c>
-      <c r="F55" s="19" t="n">
+      <c r="F55" s="21" t="n">
         <v>390</v>
       </c>
-      <c r="G55" s="19" t="n">
+      <c r="G55" s="21" t="n">
         <v>370</v>
       </c>
     </row>
@@ -5067,7 +5077,7 @@
           <t>New WIP added per AED of new development sales</t>
         </is>
       </c>
-      <c r="C56" s="24" t="n">
+      <c r="C56" s="25" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -5077,7 +5087,7 @@
           <t>Land-bank/WIP share of development cost of sales</t>
         </is>
       </c>
-      <c r="C57" s="24" t="n">
+      <c r="C57" s="25" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -5087,35 +5097,35 @@
           <t>Payables + advances cover of annual direct costs (×)</t>
         </is>
       </c>
-      <c r="C58" s="25" t="n">
+      <c r="C58" s="26" t="n">
         <v>1.86</v>
       </c>
-      <c r="D58" s="25" t="n">
+      <c r="D58" s="26" t="n">
         <v>1.7</v>
       </c>
-      <c r="E58" s="25" t="n">
+      <c r="E58" s="26" t="n">
         <v>1.55</v>
       </c>
-      <c r="F58" s="25" t="n">
+      <c r="F58" s="26" t="n">
         <v>1.45</v>
       </c>
-      <c r="G58" s="25" t="n">
+      <c r="G58" s="26" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="10" t="inlineStr">
         <is>
           <t>Cost of capital build</t>
         </is>
       </c>
-      <c r="B59" s="15" t="n"/>
-      <c r="C59" s="15" t="n"/>
-      <c r="D59" s="15" t="n"/>
-      <c r="E59" s="15" t="n"/>
-      <c r="F59" s="15" t="n"/>
-      <c r="G59" s="15" t="n"/>
-      <c r="H59" s="15" t="n"/>
+      <c r="B59" s="13" t="n"/>
+      <c r="C59" s="13" t="n"/>
+      <c r="D59" s="13" t="n"/>
+      <c r="E59" s="13" t="n"/>
+      <c r="F59" s="13" t="n"/>
+      <c r="G59" s="13" t="n"/>
+      <c r="H59" s="13" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -5123,7 +5133,7 @@
           <t>AED government bond yield (Jan-2031 T-Bond auction)</t>
         </is>
       </c>
-      <c r="C60" s="21" t="n">
+      <c r="C60" s="23" t="n">
         <v>0.0448</v>
       </c>
     </row>
@@ -5133,7 +5143,7 @@
           <t>UAE sovereign default spread (rating basis, netted out)</t>
         </is>
       </c>
-      <c r="C61" s="21" t="n">
+      <c r="C61" s="23" t="n">
         <v>0.0042</v>
       </c>
     </row>
@@ -5143,7 +5153,7 @@
           <t>Equity risk premium (UAE row, rating basis)</t>
         </is>
       </c>
-      <c r="C62" s="21" t="n">
+      <c r="C62" s="23" t="n">
         <v>0.0487</v>
       </c>
     </row>
@@ -5163,7 +5173,7 @@
           <t>6-month EIBOR (31-Mar-2026 fixing, dated)</t>
         </is>
       </c>
-      <c r="C64" s="21" t="n">
+      <c r="C64" s="23" t="n">
         <v>0.0371</v>
       </c>
     </row>
@@ -5173,7 +5183,7 @@
           <t>Marginal debt margin over 6M EIBOR</t>
         </is>
       </c>
-      <c r="C65" s="21" t="n">
+      <c r="C65" s="23" t="n">
         <v>0.0165</v>
       </c>
     </row>
@@ -5183,7 +5193,7 @@
           <t>Terminal growth</t>
         </is>
       </c>
-      <c r="C66" s="21" t="n">
+      <c r="C66" s="23" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -5193,7 +5203,7 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="C67" s="21" t="n">
+      <c r="C67" s="23" t="n">
         <v>0.08500000000000001</v>
       </c>
     </row>
@@ -5203,23 +5213,23 @@
           <t>Days from the 30-Jun-2026 valuation date to the 7-Aug anchor</t>
         </is>
       </c>
-      <c r="C68" s="19" t="n">
+      <c r="C68" s="21" t="n">
         <v>38</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="12" t="inlineStr">
+      <c r="A69" s="10" t="inlineStr">
         <is>
           <t>FY2025 disclosed anchors (audited, pasted)</t>
         </is>
       </c>
-      <c r="B69" s="15" t="n"/>
-      <c r="C69" s="15" t="n"/>
-      <c r="D69" s="15" t="n"/>
-      <c r="E69" s="15" t="n"/>
-      <c r="F69" s="15" t="n"/>
-      <c r="G69" s="15" t="n"/>
-      <c r="H69" s="15" t="n"/>
+      <c r="B69" s="13" t="n"/>
+      <c r="C69" s="13" t="n"/>
+      <c r="D69" s="13" t="n"/>
+      <c r="E69" s="13" t="n"/>
+      <c r="F69" s="13" t="n"/>
+      <c r="G69" s="13" t="n"/>
+      <c r="H69" s="13" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -5227,7 +5237,7 @@
           <t>FY2025 profit for the year (AED mn, disclosed)</t>
         </is>
       </c>
-      <c r="C70" s="19" t="n">
+      <c r="C70" s="21" t="n">
         <v>3925.705</v>
       </c>
     </row>
@@ -5237,7 +5247,7 @@
           <t>FY2025 attributable profit (AED mn, disclosed)</t>
         </is>
       </c>
-      <c r="C71" s="19" t="n">
+      <c r="C71" s="21" t="n">
         <v>4020.102</v>
       </c>
     </row>
@@ -5247,7 +5257,7 @@
           <t>FY2025 EBITDA, house basis = EBIT + D&amp;A (AED mn)</t>
         </is>
       </c>
-      <c r="C72" s="19" t="n">
+      <c r="C72" s="21" t="n">
         <v>4895.552000000001</v>
       </c>
     </row>
@@ -5257,23 +5267,23 @@
           <t>FY2025 net debt, strict basis (AED mn)</t>
         </is>
       </c>
-      <c r="C73" s="19" t="n">
+      <c r="C73" s="21" t="n">
         <v>-5852.901</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="12" t="inlineStr">
+      <c r="A74" s="10" t="inlineStr">
         <is>
           <t>Lens settings</t>
         </is>
       </c>
-      <c r="B74" s="15" t="n"/>
-      <c r="C74" s="15" t="n"/>
-      <c r="D74" s="15" t="n"/>
-      <c r="E74" s="15" t="n"/>
-      <c r="F74" s="15" t="n"/>
-      <c r="G74" s="15" t="n"/>
-      <c r="H74" s="15" t="n"/>
+      <c r="B74" s="13" t="n"/>
+      <c r="C74" s="13" t="n"/>
+      <c r="D74" s="13" t="n"/>
+      <c r="E74" s="13" t="n"/>
+      <c r="F74" s="13" t="n"/>
+      <c r="G74" s="13" t="n"/>
+      <c r="H74" s="13" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
@@ -5281,7 +5291,7 @@
           <t>Justified price/earnings (FY2026E attributable)</t>
         </is>
       </c>
-      <c r="C75" s="25" t="n">
+      <c r="C75" s="26" t="n">
         <v>7.5</v>
       </c>
     </row>
@@ -5291,7 +5301,7 @@
           <t>EV/EBITDA cross-check multiple (house judgement, unanchored)</t>
         </is>
       </c>
-      <c r="C76" s="25" t="n">
+      <c r="C76" s="26" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5301,7 +5311,7 @@
           <t>Through-cycle development sales (AED mn)</t>
         </is>
       </c>
-      <c r="C77" s="19" t="n">
+      <c r="C77" s="21" t="n">
         <v>20000</v>
       </c>
     </row>
@@ -5311,7 +5321,7 @@
           <t>Through-cycle net margin on revenue</t>
         </is>
       </c>
-      <c r="C78" s="24" t="n">
+      <c r="C78" s="25" t="n">
         <v>0.115</v>
       </c>
     </row>
@@ -5321,7 +5331,7 @@
           <t>Recurring-legs revenue base, FY2025 (AED mn, disclosed)</t>
         </is>
       </c>
-      <c r="C79" s="19" t="n">
+      <c r="C79" s="21" t="n">
         <v>6455.178</v>
       </c>
     </row>
@@ -5331,7 +5341,7 @@
           <t>Through-cycle price/earnings</t>
         </is>
       </c>
-      <c r="C80" s="25" t="n">
+      <c r="C80" s="26" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -5341,169 +5351,129 @@
           <t>Sustainable return on equity</t>
         </is>
       </c>
-      <c r="C81" s="24" t="n">
+      <c r="C81" s="25" t="n">
         <v>0.075</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Weight — discounted cash flow</t>
-        </is>
-      </c>
-      <c r="C82" s="24" t="n">
-        <v>0.4</v>
-      </c>
+      <c r="A82" s="10" t="inlineStr">
+        <is>
+          <t>Scenario driver vectors (engine re-run inputs, published for reproducibility — the pasted scenario outputs use exactly these)</t>
+        </is>
+      </c>
+      <c r="B82" s="13" t="n"/>
+      <c r="C82" s="13" t="n"/>
+      <c r="D82" s="13" t="n"/>
+      <c r="E82" s="13" t="n"/>
+      <c r="F82" s="13" t="n"/>
+      <c r="G82" s="13" t="n"/>
+      <c r="H82" s="13" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>Weight — relative</t>
-        </is>
-      </c>
-      <c r="C83" s="24" t="n">
-        <v>0.2</v>
+          <t>scenario: run-off new development sales</t>
+        </is>
+      </c>
+      <c r="C83" s="21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D83" s="21" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E83" s="21" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F83" s="21" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G83" s="21" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>Weight — normalised</t>
-        </is>
-      </c>
-      <c r="C84" s="24" t="n">
-        <v>0.2</v>
+          <t>scenario: run-off development margin</t>
+        </is>
+      </c>
+      <c r="C84" s="25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D84" s="25" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E84" s="25" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F84" s="25" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G84" s="25" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>Weight — book</t>
-        </is>
-      </c>
-      <c r="C85" s="24" t="n">
-        <v>0.2</v>
+          <t>scenario: growth-hold new development sales</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D85" s="21" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E85" s="21" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F85" s="21" t="n">
+        <v>34000</v>
+      </c>
+      <c r="G85" s="21" t="n">
+        <v>34000</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="12" t="inlineStr">
-        <is>
-          <t>Scenario driver vectors (engine re-run inputs, published for reproducibility — the pasted scenario outputs use exactly these)</t>
-        </is>
-      </c>
-      <c r="B86" s="15" t="n"/>
-      <c r="C86" s="15" t="n"/>
-      <c r="D86" s="15" t="n"/>
-      <c r="E86" s="15" t="n"/>
-      <c r="F86" s="15" t="n"/>
-      <c r="G86" s="15" t="n"/>
-      <c r="H86" s="15" t="n"/>
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>scenario: growth-hold development margin</t>
+        </is>
+      </c>
+      <c r="C86" s="25" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D86" s="25" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E86" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F86" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G86" s="25" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>scenario: run-off new development sales</t>
-        </is>
-      </c>
-      <c r="C87" s="19" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D87" s="19" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E87" s="19" t="n">
-        <v>11000</v>
-      </c>
-      <c r="F87" s="19" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G87" s="19" t="n">
-        <v>8000</v>
+          <t>scenario: Egypt stress — non-UAE revenue share (note 5)</t>
+        </is>
+      </c>
+      <c r="C87" s="25" t="n">
+        <v>0.170797409390457</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>scenario: run-off development margin</t>
-        </is>
-      </c>
-      <c r="C88" s="24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D88" s="24" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E88" s="24" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F88" s="24" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="G88" s="24" t="n">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="6" t="inlineStr">
-        <is>
-          <t>scenario: growth-hold new development sales</t>
-        </is>
-      </c>
-      <c r="C89" s="19" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D89" s="19" t="n">
-        <v>34000</v>
-      </c>
-      <c r="E89" s="19" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F89" s="19" t="n">
-        <v>34000</v>
-      </c>
-      <c r="G89" s="19" t="n">
-        <v>34000</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>scenario: growth-hold development margin</t>
-        </is>
-      </c>
-      <c r="C90" s="24" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D90" s="24" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E90" s="24" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="F90" s="24" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G90" s="24" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>scenario: Egypt stress — non-UAE revenue share (note 5)</t>
-        </is>
-      </c>
-      <c r="C91" s="24" t="n">
-        <v>0.170797409390457</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
-        <is>
           <t>scenario: Egypt country risk premium (Damodaran)</t>
         </is>
       </c>
-      <c r="C92" s="21" t="n">
+      <c r="C88" s="23" t="n">
         <v>0.09710000000000001</v>
       </c>
     </row>
@@ -5554,7 +5524,7 @@
           <t>FY2025 G&amp;A + S&amp;M (audited, for the load allocation)</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="21" t="n">
         <v>1813.687</v>
       </c>
     </row>
@@ -5581,11 +5551,11 @@
           <t>Real Estate Development</t>
         </is>
       </c>
-      <c r="B6" s="17">
+      <c r="B6" s="19">
         <f>Segments!C5-$B$4*Segments!B5/Segments!B10</f>
         <v/>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="19">
         <f>MAX(B6,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
         <v/>
       </c>
@@ -5596,11 +5566,11 @@
           <t>Asset &amp; Investment Management</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="19">
         <f>Segments!C6-$B$4*Segments!B6/Segments!B10</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="19">
         <f>MAX(B7,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
         <v/>
       </c>
@@ -5611,11 +5581,11 @@
           <t>Hospitality</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="19">
         <f>Segments!C7-$B$4*Segments!B7/Segments!B10</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="19">
         <f>MAX(B8,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
         <v/>
       </c>
@@ -5626,29 +5596,29 @@
           <t>Events, Catering &amp; Tourism</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="19">
         <f>Segments!C8-$B$4*Segments!B8/Segments!B10</f>
         <v/>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="19">
         <f>MAX(B9,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Enterprise value (links to DCF)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n"/>
-      <c r="C10" s="26">
+      <c r="B10" s="13" t="n"/>
+      <c r="C10" s="27">
         <f>DCF!C48</f>
         <v/>
       </c>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -5656,7 +5626,7 @@
           <t>Terminal value share of enterprise value</t>
         </is>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <f>DCF!C49</f>
         <v/>
       </c>
@@ -5667,7 +5637,7 @@
           <t>+ Unrestricted cash (disclosed)</t>
         </is>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="20">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
@@ -5678,7 +5648,7 @@
           <t>− Gross debt incl. related-party loan</t>
         </is>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="20">
         <f>-Assumptions!$C$10</f>
         <v/>
       </c>
@@ -5689,7 +5659,7 @@
           <t>− Lease liabilities</t>
         </is>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="20">
         <f>-Assumptions!$C$11</f>
         <v/>
       </c>
@@ -5700,7 +5670,7 @@
           <t>+ Associates &amp; JVs</t>
         </is>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="20">
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
@@ -5711,7 +5681,7 @@
           <t>+ Financial assets</t>
         </is>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="20">
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
@@ -5722,25 +5692,25 @@
           <t>− NCI (capitalised, links to DCF)</t>
         </is>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="20">
         <f>DCF!C58</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>Equity attributable → per share → at anchor</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="26">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="27">
         <f>C10+SUM(C12:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
+      <c r="D18" s="13" t="n"/>
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="13" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -5748,7 +5718,7 @@
           <t>per share, 30-Jun-2026</t>
         </is>
       </c>
-      <c r="C19" s="10">
+      <c r="C19" s="16">
         <f>C18/Assumptions!$C$5</f>
         <v/>
       </c>
@@ -5759,7 +5729,7 @@
           <t>per share at the 7-Aug-2026 anchor</t>
         </is>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="24">
         <f>C19*DCF!C61</f>
         <v/>
       </c>
@@ -5857,20 +5827,20 @@
           <t>Real Estate Development</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="21" t="n">
         <v>7403.313</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>3232.891</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="9">
         <f>C5/B5</f>
         <v/>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="21" t="n">
         <v>2547.573</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="21" t="n">
         <v>55738.581</v>
       </c>
     </row>
@@ -5880,20 +5850,20 @@
           <t>Asset &amp; Investment Management</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="21" t="n">
         <v>654.658</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="21" t="n">
         <v>421.083</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="9">
         <f>C6/B6</f>
         <v/>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="21" t="n">
         <v>685.082</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="21" t="n">
         <v>11095.849</v>
       </c>
     </row>
@@ -5903,20 +5873,20 @@
           <t>Hospitality</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="21" t="n">
         <v>791.771</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="21" t="n">
         <v>210.893</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="9">
         <f>C7/B7</f>
         <v/>
       </c>
-      <c r="E7" s="19" t="n">
+      <c r="E7" s="21" t="n">
         <v>-69.15000000000001</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="21" t="n">
         <v>4601.757</v>
       </c>
     </row>
@@ -5926,20 +5896,20 @@
           <t>Events, Catering &amp; Tourism</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
+      <c r="B8" s="21" t="n">
         <v>5008.749</v>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="21" t="n">
         <v>1325.029</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <f>C8/B8</f>
         <v/>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="21" t="n">
         <v>1061.602</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="21" t="n">
         <v>14118.268</v>
       </c>
     </row>
@@ -5949,32 +5919,32 @@
           <t>Others / eliminations</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="21" t="n">
         <v>-29.622</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="21" t="n">
         <v>-164.637</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Group FY2025</t>
         </is>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <f>SUM(B5:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="15" t="n"/>
-      <c r="E10" s="15" t="n"/>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
-      <c r="H10" s="15" t="n"/>
+      <c r="D10" s="13" t="n"/>
+      <c r="E10" s="13" t="n"/>
+      <c r="F10" s="13" t="n"/>
+      <c r="G10" s="13" t="n"/>
+      <c r="H10" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -6014,23 +5984,23 @@
           <t>Opening development backlog</t>
         </is>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="20">
         <f>Assumptions!$C$7</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="19">
         <f>B16</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="19">
         <f>C16</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="19">
         <f>D16</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="19">
         <f>E16</f>
         <v/>
       </c>
@@ -6041,23 +6011,23 @@
           <t>New development sales</t>
         </is>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="20">
         <f>Assumptions!$C$26</f>
         <v/>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="20">
         <f>Assumptions!$D$26</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="20">
         <f>Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="20">
         <f>Assumptions!$F$26</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="20">
         <f>Assumptions!$G$26</f>
         <v/>
       </c>
@@ -6068,23 +6038,23 @@
           <t>Development revenue recognised (conv × opening)</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="19">
         <f>Assumptions!$C$25*B13</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="19">
         <f>Assumptions!$D$25*C13</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="19">
         <f>Assumptions!$E$25*D13</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="19">
         <f>Assumptions!$F$25*E13</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="19">
         <f>Assumptions!$G$25*F13</f>
         <v/>
       </c>
@@ -6095,23 +6065,23 @@
           <t>Closing backlog</t>
         </is>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="19">
         <f>B13+B14-B15</f>
         <v/>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="19">
         <f>C13+C14-C15</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="19">
         <f>D13+D14-D15</f>
         <v/>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="19">
         <f>E13+E14-E15</f>
         <v/>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="19">
         <f>F13+F14-F15</f>
         <v/>
       </c>
@@ -6122,23 +6092,23 @@
           <t>Land and plot sales</t>
         </is>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="20">
         <f>Assumptions!$C$27</f>
         <v/>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="20">
         <f>Assumptions!$D$27</f>
         <v/>
       </c>
-      <c r="D17" s="18">
+      <c r="D17" s="20">
         <f>Assumptions!$E$27</f>
         <v/>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="20">
         <f>Assumptions!$F$27</f>
         <v/>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="20">
         <f>Assumptions!$G$27</f>
         <v/>
       </c>
@@ -6149,23 +6119,23 @@
           <t>Real Estate Development revenue</t>
         </is>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="28">
         <f>B15+B17</f>
         <v/>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="28">
         <f>C15+C17</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>D15+D17</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>E15+E17</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="28">
         <f>F15+F17</f>
         <v/>
       </c>
@@ -6208,23 +6178,23 @@
           <t>Real Estate Development</t>
         </is>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="19">
         <f>B18</f>
         <v/>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="19">
         <f>C18</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="19">
         <f>D18</f>
         <v/>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="19">
         <f>E18</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="19">
         <f>F18</f>
         <v/>
       </c>
@@ -6235,23 +6205,23 @@
           <t>Asset &amp; Investment Management</t>
         </is>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="20">
         <f>Assumptions!$C$30</f>
         <v/>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="19">
         <f>(Assumptions!$C$38+Assumptions!$C$30)*(1+Assumptions!$D$29)</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="19">
         <f>C22*(1+Assumptions!$E$29)</f>
         <v/>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="19">
         <f>D22*(1+Assumptions!$F$29)</f>
         <v/>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="19">
         <f>E22*(1+Assumptions!$G$29)</f>
         <v/>
       </c>
@@ -6262,23 +6232,23 @@
           <t>Hospitality</t>
         </is>
       </c>
-      <c r="B23" s="18">
+      <c r="B23" s="20">
         <f>Assumptions!$C$33</f>
         <v/>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="19">
         <f>(Assumptions!$C$39+Assumptions!$C$33)*(1+Assumptions!$D$32)</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="19">
         <f>C23*(1+Assumptions!$E$32)</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="19">
         <f>D23*(1+Assumptions!$F$32)</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="19">
         <f>E23*(1+Assumptions!$G$32)</f>
         <v/>
       </c>
@@ -6289,23 +6259,23 @@
           <t>Events, Catering &amp; Tourism</t>
         </is>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="20">
         <f>Assumptions!$C$36</f>
         <v/>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="19">
         <f>(Assumptions!$C$40+Assumptions!$C$36)*(1+Assumptions!$D$35)</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="19">
         <f>C24*(1+Assumptions!$E$35)</f>
         <v/>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="19">
         <f>D24*(1+Assumptions!$F$35)</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="19">
         <f>E24*(1+Assumptions!$G$35)</f>
         <v/>
       </c>
@@ -6316,23 +6286,23 @@
           <t>Others / eliminations (half-year in the stub)</t>
         </is>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="20">
         <f>Assumptions!$C$41*0.5</f>
         <v/>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="20">
         <f>Assumptions!$C$41*1.0</f>
         <v/>
       </c>
-      <c r="D25" s="18">
+      <c r="D25" s="20">
         <f>Assumptions!$C$41*1.0</f>
         <v/>
       </c>
-      <c r="E25" s="18">
+      <c r="E25" s="20">
         <f>Assumptions!$C$41*1.0</f>
         <v/>
       </c>
-      <c r="F25" s="18">
+      <c r="F25" s="20">
         <f>Assumptions!$C$41*1.0</f>
         <v/>
       </c>
@@ -6343,23 +6313,23 @@
           <t>Group revenue</t>
         </is>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="28">
         <f>SUM(B21:B25)</f>
         <v/>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="28">
         <f>SUM(C21:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="28">
         <f>SUM(D21:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="28">
         <f>SUM(E21:E25)</f>
         <v/>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="28">
         <f>SUM(F21:F25)</f>
         <v/>
       </c>
@@ -6402,23 +6372,23 @@
           <t>Real Estate Development</t>
         </is>
       </c>
-      <c r="B29" s="17">
+      <c r="B29" s="19">
         <f>B21*Assumptions!$C$28</f>
         <v/>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="19">
         <f>C21*Assumptions!$D$28</f>
         <v/>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="19">
         <f>D21*Assumptions!$E$28</f>
         <v/>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="19">
         <f>E21*Assumptions!$F$28</f>
         <v/>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="19">
         <f>F21*Assumptions!$G$28</f>
         <v/>
       </c>
@@ -6429,23 +6399,23 @@
           <t>Asset &amp; Investment Management</t>
         </is>
       </c>
-      <c r="B30" s="17">
+      <c r="B30" s="19">
         <f>B22*Assumptions!$C$31</f>
         <v/>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="19">
         <f>C22*Assumptions!$D$31</f>
         <v/>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="19">
         <f>D22*Assumptions!$E$31</f>
         <v/>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="19">
         <f>E22*Assumptions!$F$31</f>
         <v/>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="19">
         <f>F22*Assumptions!$G$31</f>
         <v/>
       </c>
@@ -6456,23 +6426,23 @@
           <t>Hospitality</t>
         </is>
       </c>
-      <c r="B31" s="17">
+      <c r="B31" s="19">
         <f>B23*Assumptions!$C$34</f>
         <v/>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="19">
         <f>C23*Assumptions!$D$34</f>
         <v/>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="19">
         <f>D23*Assumptions!$E$34</f>
         <v/>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="19">
         <f>E23*Assumptions!$F$34</f>
         <v/>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="19">
         <f>F23*Assumptions!$G$34</f>
         <v/>
       </c>
@@ -6483,23 +6453,23 @@
           <t>Events, Catering &amp; Tourism</t>
         </is>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="19">
         <f>B24*Assumptions!$C$37</f>
         <v/>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="19">
         <f>C24*Assumptions!$D$37</f>
         <v/>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="19">
         <f>D24*Assumptions!$E$37</f>
         <v/>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="19">
         <f>E24*Assumptions!$F$37</f>
         <v/>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="19">
         <f>F24*Assumptions!$G$37</f>
         <v/>
       </c>
@@ -6510,23 +6480,23 @@
           <t>Others (half-year in the stub)</t>
         </is>
       </c>
-      <c r="B33" s="18">
+      <c r="B33" s="20">
         <f>Assumptions!$C$42*0.5</f>
         <v/>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="20">
         <f>Assumptions!$C$42*1.0</f>
         <v/>
       </c>
-      <c r="D33" s="18">
+      <c r="D33" s="20">
         <f>Assumptions!$C$42*1.0</f>
         <v/>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="20">
         <f>Assumptions!$C$42*1.0</f>
         <v/>
       </c>
-      <c r="F33" s="18">
+      <c r="F33" s="20">
         <f>Assumptions!$C$42*1.0</f>
         <v/>
       </c>
@@ -6537,23 +6507,23 @@
           <t>Group gross profit</t>
         </is>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="28">
         <f>SUM(B29:B33)</f>
         <v/>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="28">
         <f>SUM(C29:C33)</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="28">
         <f>SUM(D29:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="28">
         <f>SUM(E29:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="27">
+      <c r="F34" s="28">
         <f>SUM(F29:F33)</f>
         <v/>
       </c>
@@ -6564,23 +6534,23 @@
           <t>Group gross margin (output)</t>
         </is>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="9">
         <f>B34/B26</f>
         <v/>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="9">
         <f>C34/C26</f>
         <v/>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="9">
         <f>D34/D26</f>
         <v/>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="9">
         <f>E34/E26</f>
         <v/>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="9">
         <f>F34/F26</f>
         <v/>
       </c>
@@ -6646,7 +6616,7 @@
           <t>FY2026E attributable profit = H1 actual + H2 model</t>
         </is>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="20">
         <f>Assumptions!$C$21+'Income Statement'!F17</f>
         <v/>
       </c>
@@ -6657,7 +6627,7 @@
           <t>Justified P/E × FY2026E EPS</t>
         </is>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="16">
         <f>Assumptions!$C$75*C5/Assumptions!$C$5</f>
         <v/>
       </c>
@@ -6668,7 +6638,7 @@
           <t>FY2026E EBITDA (H1 adjusted-EBITDA + H2 model)</t>
         </is>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="20">
         <f>Assumptions!$C$22+DCF!B13</f>
         <v/>
       </c>
@@ -6679,26 +6649,26 @@
           <t>EV/EBITDA cross-check (house multiple, unanchored — labelled)</t>
         </is>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="16">
         <f>(Assumptions!$C$76*C7+Assumptions!$C$8-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-MAX(Assumptions!$C$14,0.02*(Assumptions!$C$76*C7+Assumptions!$C$8-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-Assumptions!$C$14)))/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Relative lens (P/E leg)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="13">
+      <c r="B11" s="13" t="n"/>
+      <c r="C11" s="11">
         <f>C6</f>
         <v/>
       </c>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="D11" s="13" t="n"/>
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="13" t="n"/>
+      <c r="G11" s="13" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6706,11 +6676,11 @@
           <t>bear / bull (lens scaled to the peer-set floor 4.73x and ceiling 8.10x)</t>
         </is>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="16">
         <f>C11*4.73/Assumptions!$C$75</f>
         <v/>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="16">
         <f>C11*8.1/Assumptions!$C$75</f>
         <v/>
       </c>
@@ -6733,7 +6703,7 @@
           <t>Trailing P/E on FY2025 attributable profit</t>
         </is>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="29">
         <f>DCF!C33/Assumptions!$C$71</f>
         <v/>
       </c>
@@ -6744,7 +6714,7 @@
           <t>Trailing P/E on FY2025 group profit (dual-framed)</t>
         </is>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="29">
         <f>DCF!C33/Assumptions!$C$70</f>
         <v/>
       </c>
@@ -6755,7 +6725,7 @@
           <t>Trailing EV/EBITDA (mktcap + FY2025 strict net debt over house EBITDA)</t>
         </is>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="29">
         <f>(DCF!C33+Assumptions!$C$73)/Assumptions!$C$72</f>
         <v/>
       </c>
@@ -6778,7 +6748,7 @@
           <t>Through-cycle revenue = 85% × cycle sales + recurring legs × 1.15</t>
         </is>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="19">
         <f>Assumptions!$C$77*0.85+Assumptions!$C$79*1.15</f>
         <v/>
       </c>
@@ -6789,7 +6759,7 @@
           <t>Through-cycle net margin</t>
         </is>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="17">
         <f>Assumptions!$C$78</f>
         <v/>
       </c>
@@ -6800,7 +6770,7 @@
           <t>Normalised net profit</t>
         </is>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="19">
         <f>C20*C21</f>
         <v/>
       </c>
@@ -6811,26 +6781,26 @@
           <t>Normalised EPS</t>
         </is>
       </c>
-      <c r="C23" s="10">
+      <c r="C23" s="16">
         <f>C22/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>Normalised lens = EPS × through-cycle P/E</t>
         </is>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="24">
         <f>C23*Assumptions!$C$80</f>
         <v/>
       </c>
-      <c r="E28" s="10">
+      <c r="E28" s="16">
         <f>C23*6</f>
         <v/>
       </c>
-      <c r="F28" s="10">
+      <c r="F28" s="16">
         <f>C23*10.5</f>
         <v/>
       </c>
@@ -6853,7 +6823,7 @@
           <t>Book value per share (30-Jun-2026 attributable equity)</t>
         </is>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="16">
         <f>Assumptions!$C$15/Assumptions!$C$5</f>
         <v/>
       </c>
@@ -6864,26 +6834,26 @@
           <t>Justified P/B = (ROE − g)/(Ke − g)</t>
         </is>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="29">
         <f>(Assumptions!$C$81-Assumptions!$C$66)/(DCF!C30-Assumptions!$C$66)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="22" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Book lens = BVPS × justified P/B × anchor roll</t>
         </is>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="24">
         <f>C31*C32*DCF!C61</f>
         <v/>
       </c>
-      <c r="E36" s="10">
+      <c r="E36" s="16">
         <f>C31*((0.055-Assumptions!$C$66)/(DCF!C30-Assumptions!$C$66))*DCF!C61</f>
         <v/>
       </c>
-      <c r="F36" s="10">
+      <c r="F36" s="16">
         <f>C31*((0.095-Assumptions!$C$66)/(DCF!C30-Assumptions!$C$66))*DCF!C61</f>
         <v/>
       </c>
@@ -6971,23 +6941,23 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="20">
         <f>Segments!B26</f>
         <v/>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="20">
         <f>Segments!C26</f>
         <v/>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="20">
         <f>Segments!D26</f>
         <v/>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="20">
         <f>Segments!E26</f>
         <v/>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="20">
         <f>Segments!F26</f>
         <v/>
       </c>
@@ -6998,23 +6968,23 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="20">
         <f>Segments!B34</f>
         <v/>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="20">
         <f>Segments!C34</f>
         <v/>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="20">
         <f>Segments!D34</f>
         <v/>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="20">
         <f>Segments!E34</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="20">
         <f>Segments!F34</f>
         <v/>
       </c>
@@ -7025,23 +6995,23 @@
           <t>General &amp; administrative</t>
         </is>
       </c>
-      <c r="B7" s="17">
+      <c r="B7" s="19">
         <f>-Assumptions!$C$43*B5</f>
         <v/>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="19">
         <f>-Assumptions!$D$43*C5</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="19">
         <f>-Assumptions!$E$43*D5</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="19">
         <f>-Assumptions!$F$43*E5</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="19">
         <f>-Assumptions!$G$43*F5</f>
         <v/>
       </c>
@@ -7052,23 +7022,23 @@
           <t>Selling &amp; marketing</t>
         </is>
       </c>
-      <c r="B8" s="17">
+      <c r="B8" s="19">
         <f>-Assumptions!$C$44*B5</f>
         <v/>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="19">
         <f>-Assumptions!$D$44*C5</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="19">
         <f>-Assumptions!$E$44*D5</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="19">
         <f>-Assumptions!$F$44*E5</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="19">
         <f>-Assumptions!$G$44*F5</f>
         <v/>
       </c>
@@ -7079,23 +7049,23 @@
           <t>Investment and other income</t>
         </is>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="20">
         <f>Assumptions!$C$45</f>
         <v/>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="20">
         <f>Assumptions!$D$45</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="20">
         <f>Assumptions!$E$45</f>
         <v/>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="20">
         <f>Assumptions!$F$45</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="20">
         <f>Assumptions!$G$45</f>
         <v/>
       </c>
@@ -7106,23 +7076,23 @@
           <t>EBIT (post-D&amp;A, ex-fair-value items)</t>
         </is>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="28">
         <f>SUM(B6:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <f>SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="28">
         <f>SUM(D6:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="28">
         <f>SUM(E6:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <f>SUM(F6:F9)</f>
         <v/>
       </c>
@@ -7133,23 +7103,23 @@
           <t>EBITDA margin (output)</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <f>(B10+B12)/B5</f>
         <v/>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="9">
         <f>(C10+C12)/C5</f>
         <v/>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="9">
         <f>(D10+D12)/D5</f>
         <v/>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="9">
         <f>(E10+E12)/E5</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="9">
         <f>(F10+F12)/F5</f>
         <v/>
       </c>
@@ -7160,23 +7130,23 @@
           <t>Depreciation &amp; amortisation (asset-base)</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="19">
         <f>Assumptions!$C$46*(B21+Assumptions!$C$47/2)*0.5</f>
         <v/>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="19">
         <f>Assumptions!$C$46*(C21+Assumptions!$D$47/2)*1.0</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="19">
         <f>Assumptions!$C$46*(D21+Assumptions!$E$47/2)*1.0</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="19">
         <f>Assumptions!$C$46*(E21+Assumptions!$F$47/2)*1.0</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="19">
         <f>Assumptions!$C$46*(F21+Assumptions!$G$47/2)*1.0</f>
         <v/>
       </c>
@@ -7187,23 +7157,23 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="19">
         <f>B10+B12</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="19">
         <f>C10+C12</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="19">
         <f>D10+D12</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="19">
         <f>E10+E12</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="19">
         <f>F10+F12</f>
         <v/>
       </c>
@@ -7214,23 +7184,23 @@
           <t>NOPAT = EBIT × (1 − t)</t>
         </is>
       </c>
-      <c r="B14" s="17">
+      <c r="B14" s="19">
         <f>B10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="19">
         <f>C10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="19">
         <f>D10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="19">
         <f>E10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="19">
         <f>F10*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
@@ -7241,23 +7211,23 @@
           <t>+ D&amp;A</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="19">
         <f>B12</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="19">
         <f>C12</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="19">
         <f>D12</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="19">
         <f>E12</f>
         <v/>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="19">
         <f>F12</f>
         <v/>
       </c>
@@ -7268,23 +7238,23 @@
           <t>− Capital expenditure</t>
         </is>
       </c>
-      <c r="B16" s="17">
+      <c r="B16" s="19">
         <f>-Assumptions!$C$47</f>
         <v/>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="19">
         <f>-Assumptions!$D$47</f>
         <v/>
       </c>
-      <c r="D16" s="17">
+      <c r="D16" s="19">
         <f>-Assumptions!$E$47</f>
         <v/>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="19">
         <f>-Assumptions!$F$47</f>
         <v/>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="19">
         <f>-Assumptions!$G$47</f>
         <v/>
       </c>
@@ -7295,23 +7265,23 @@
           <t>− Δ working capital (from components below)</t>
         </is>
       </c>
-      <c r="B17" s="17">
+      <c r="B17" s="19">
         <f>-B26</f>
         <v/>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="19">
         <f>-C26</f>
         <v/>
       </c>
-      <c r="D17" s="17">
+      <c r="D17" s="19">
         <f>-D26</f>
         <v/>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="19">
         <f>-E26</f>
         <v/>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="19">
         <f>-F26</f>
         <v/>
       </c>
@@ -7322,23 +7292,23 @@
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="B18" s="27">
+      <c r="B18" s="28">
         <f>SUM(B14:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="28">
         <f>SUM(C14:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="27">
+      <c r="D18" s="28">
         <f>SUM(D14:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="27">
+      <c r="E18" s="28">
         <f>SUM(E14:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="28">
         <f>SUM(F14:F17)</f>
         <v/>
       </c>
@@ -7349,23 +7319,23 @@
           <t>Discount factor (period-end from 30-Jun-2026)</t>
         </is>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <f>1/(1+$C$36)^0.5</f>
         <v/>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <f>1/(1+$C$36)^1.5</f>
         <v/>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <f>1/(1+$C$36)^2.5</f>
         <v/>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <f>1/(1+$C$36)^3.5</f>
         <v/>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <f>1/(1+$C$36)^4.5</f>
         <v/>
       </c>
@@ -7376,23 +7346,23 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B20" s="17">
+      <c r="B20" s="19">
         <f>B18*B19</f>
         <v/>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="19">
         <f>C18*C19</f>
         <v/>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="19">
         <f>D18*D19</f>
         <v/>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="19">
         <f>E18*E19</f>
         <v/>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="19">
         <f>F18*F19</f>
         <v/>
       </c>
@@ -7403,23 +7373,23 @@
           <t>Depreciable asset base (opening)</t>
         </is>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="20">
         <f>Assumptions!$C$23</f>
         <v/>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="19">
         <f>B21+Assumptions!$C$47-B12</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="19">
         <f>C21+Assumptions!$D$47-C12</f>
         <v/>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="19">
         <f>D21+Assumptions!$E$47-D12</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="19">
         <f>E21+Assumptions!$F$47-E12</f>
         <v/>
       </c>
@@ -7430,23 +7400,23 @@
           <t>Receivables (days × revenue)</t>
         </is>
       </c>
-      <c r="B22" s="17">
+      <c r="B22" s="19">
         <f>Assumptions!$C$55/365*(Assumptions!$C$19+B5)</f>
         <v/>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="19">
         <f>Assumptions!$D$55/365*C5</f>
         <v/>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="19">
         <f>Assumptions!$E$55/365*D5</f>
         <v/>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="19">
         <f>Assumptions!$F$55/365*E5</f>
         <v/>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="19">
         <f>Assumptions!$G$55/365*F5</f>
         <v/>
       </c>
@@ -7457,23 +7427,23 @@
           <t>Inventories + WIP (roll)</t>
         </is>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="19">
         <f>Assumptions!$C$17+Assumptions!$C$56*Assumptions!$C$26-Assumptions!$C$57*Segments!B18*(1-Assumptions!$C$28)</f>
         <v/>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="19">
         <f>B23+Assumptions!$C$56*Assumptions!$D$26-Assumptions!$C$57*Segments!C18*(1-Assumptions!$D$28)</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="19">
         <f>C23+Assumptions!$C$56*Assumptions!$E$26-Assumptions!$C$57*Segments!D18*(1-Assumptions!$E$28)</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="19">
         <f>D23+Assumptions!$C$56*Assumptions!$F$26-Assumptions!$C$57*Segments!E18*(1-Assumptions!$F$28)</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="19">
         <f>E23+Assumptions!$C$56*Assumptions!$G$26-Assumptions!$C$57*Segments!F18*(1-Assumptions!$G$28)</f>
         <v/>
       </c>
@@ -7484,23 +7454,23 @@
           <t>Payables + advances (cover × costs)</t>
         </is>
       </c>
-      <c r="B24" s="17">
+      <c r="B24" s="19">
         <f>Assumptions!$C$58*(Assumptions!$C$19+B5-Assumptions!$C$20-B6)</f>
         <v/>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="19">
         <f>Assumptions!$D$58*(C5-C6)</f>
         <v/>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="19">
         <f>Assumptions!$E$58*(D5-D6)</f>
         <v/>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="19">
         <f>Assumptions!$F$58*(E5-E6)</f>
         <v/>
       </c>
-      <c r="F24" s="17">
+      <c r="F24" s="19">
         <f>Assumptions!$G$58*(F5-F6)</f>
         <v/>
       </c>
@@ -7511,23 +7481,23 @@
           <t>Net working capital</t>
         </is>
       </c>
-      <c r="B25" s="17">
+      <c r="B25" s="19">
         <f>B22+B23-B24</f>
         <v/>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="19">
         <f>C22+C23-C24</f>
         <v/>
       </c>
-      <c r="D25" s="17">
+      <c r="D25" s="19">
         <f>D22+D23-D24</f>
         <v/>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="19">
         <f>E22+E23-E24</f>
         <v/>
       </c>
-      <c r="F25" s="17">
+      <c r="F25" s="19">
         <f>F22+F23-F24</f>
         <v/>
       </c>
@@ -7538,40 +7508,40 @@
           <t>Δ working capital</t>
         </is>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="19">
         <f>B25-(Assumptions!$C$16+Assumptions!$C$17-Assumptions!$C$18)</f>
         <v/>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="19">
         <f>C25-B25</f>
         <v/>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="19">
         <f>D25-C25</f>
         <v/>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="19">
         <f>E25-D25</f>
         <v/>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="19">
         <f>F25-E25</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Cost of capital — built on the sheet</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="15" t="n"/>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
+      <c r="B28" s="13" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="13" t="n"/>
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="13" t="n"/>
+      <c r="G28" s="13" t="n"/>
+      <c r="H28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -7579,7 +7549,7 @@
           <t>Normalised risk-free rate rf* = AED yield − sovereign spread</t>
         </is>
       </c>
-      <c r="C29" s="20">
+      <c r="C29" s="22">
         <f>Assumptions!$C$60-Assumptions!$C$61</f>
         <v/>
       </c>
@@ -7590,7 +7560,7 @@
           <t>Cost of equity Ke = rf* + β × ERP (β from the panel-proxy regression)</t>
         </is>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <f>C29+Assumptions!$C$63*Assumptions!$C$62</f>
         <v/>
       </c>
@@ -7601,7 +7571,7 @@
           <t>Marginal cost of debt Kd = 6M EIBOR + margin</t>
         </is>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <f>Assumptions!$C$64+Assumptions!$C$65</f>
         <v/>
       </c>
@@ -7612,7 +7582,7 @@
           <t>Kd after tax</t>
         </is>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="31">
         <f>C31*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
@@ -7623,7 +7593,7 @@
           <t>Market capitalisation (spot × shares)</t>
         </is>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="19">
         <f>Assumptions!$C$4*Assumptions!$C$5</f>
         <v/>
       </c>
@@ -7634,7 +7604,7 @@
           <t>Equity weight E/(E+D), debt at the 30-Jun-2026 book</t>
         </is>
       </c>
-      <c r="C34" s="30">
+      <c r="C34" s="31">
         <f>C33/(C33+Assumptions!$C$10)</f>
         <v/>
       </c>
@@ -7645,7 +7615,7 @@
           <t>Debt weight D/(E+D)</t>
         </is>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <f>1-C34</f>
         <v/>
       </c>
@@ -7656,7 +7626,7 @@
           <t>Cost of capital (explicit window)</t>
         </is>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="32">
         <f>C34*C30+C35*C32</f>
         <v/>
       </c>
@@ -7667,7 +7637,7 @@
           <t>Terminal debt weight — DERIVED from the FY2030E balance sheet</t>
         </is>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <f>'Balance Sheet'!J12/('Balance Sheet'!J12+'Balance Sheet'!J14+'Balance Sheet'!J15)</f>
         <v/>
       </c>
@@ -7678,24 +7648,24 @@
           <t>Terminal cost of capital (derived weights)</t>
         </is>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <f>(1-C37)*C30+C37*C31*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>Terminal block — reinvestment derived</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
-      <c r="G40" s="15" t="n"/>
-      <c r="H40" s="15" t="n"/>
+      <c r="B40" s="13" t="n"/>
+      <c r="C40" s="13" t="n"/>
+      <c r="D40" s="13" t="n"/>
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="13" t="n"/>
+      <c r="G40" s="13" t="n"/>
+      <c r="H40" s="13" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -7703,7 +7673,7 @@
           <t>Terminal growth g</t>
         </is>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="22">
         <f>Assumptions!$C$66</f>
         <v/>
       </c>
@@ -7714,7 +7684,7 @@
           <t>Terminal return on invested capital</t>
         </is>
       </c>
-      <c r="C42" s="20">
+      <c r="C42" s="22">
         <f>Assumptions!$C$67</f>
         <v/>
       </c>
@@ -7725,7 +7695,7 @@
           <t>Reinvestment rate = g / ROIC</t>
         </is>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <f>C41/C42</f>
         <v/>
       </c>
@@ -7736,7 +7706,7 @@
           <t>Terminal NOPAT = FY2030E NOPAT × (1+g)</t>
         </is>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="19">
         <f>F14*(1+C41)</f>
         <v/>
       </c>
@@ -7747,7 +7717,7 @@
           <t>Terminal value = NOPAT × (1−RR) / (WACCterm − g)</t>
         </is>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="19">
         <f>C44*(1-C43)/(C38-C41)</f>
         <v/>
       </c>
@@ -7758,7 +7728,7 @@
           <t>PV of terminal value (year-4.5 factor)</t>
         </is>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="19">
         <f>C45*F19</f>
         <v/>
       </c>
@@ -7769,7 +7739,7 @@
           <t>PV of explicit periods</t>
         </is>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="19">
         <f>SUM(B20:F20)</f>
         <v/>
       </c>
@@ -7780,7 +7750,7 @@
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="C48" s="27">
+      <c r="C48" s="28">
         <f>C46+C47</f>
         <v/>
       </c>
@@ -7791,24 +7761,24 @@
           <t>Terminal value share of enterprise value</t>
         </is>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="33">
         <f>C46/C48</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>EV → equity bridge (30-Jun-2026, available-cash basis)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="n"/>
-      <c r="C51" s="15" t="n"/>
-      <c r="D51" s="15" t="n"/>
-      <c r="E51" s="15" t="n"/>
-      <c r="F51" s="15" t="n"/>
-      <c r="G51" s="15" t="n"/>
-      <c r="H51" s="15" t="n"/>
+      <c r="B51" s="13" t="n"/>
+      <c r="C51" s="13" t="n"/>
+      <c r="D51" s="13" t="n"/>
+      <c r="E51" s="13" t="n"/>
+      <c r="F51" s="13" t="n"/>
+      <c r="G51" s="13" t="n"/>
+      <c r="H51" s="13" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -7816,7 +7786,7 @@
           <t>+ Unrestricted (available) cash — disclosed</t>
         </is>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="20">
         <f>Assumptions!$C$8</f>
         <v/>
       </c>
@@ -7834,7 +7804,7 @@
           <t>− Gross debt incl. related-party loan</t>
         </is>
       </c>
-      <c r="C54" s="18">
+      <c r="C54" s="20">
         <f>-Assumptions!$C$10</f>
         <v/>
       </c>
@@ -7845,7 +7815,7 @@
           <t>− Lease liabilities</t>
         </is>
       </c>
-      <c r="C55" s="18">
+      <c r="C55" s="20">
         <f>-Assumptions!$C$11</f>
         <v/>
       </c>
@@ -7856,7 +7826,7 @@
           <t>+ Associates &amp; JVs at carrying value</t>
         </is>
       </c>
-      <c r="C56" s="18">
+      <c r="C56" s="20">
         <f>Assumptions!$C$12</f>
         <v/>
       </c>
@@ -7867,7 +7837,7 @@
           <t>+ Investments in financial assets</t>
         </is>
       </c>
-      <c r="C57" s="18">
+      <c r="C57" s="20">
         <f>Assumptions!$C$13</f>
         <v/>
       </c>
@@ -7878,7 +7848,7 @@
           <t>− Non-controlling interests, capitalised at share of equity value (MAX of book and 2%)</t>
         </is>
       </c>
-      <c r="C58" s="17">
+      <c r="C58" s="19">
         <f>-MAX(Assumptions!$C$14,0.02*(C48+C52-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-Assumptions!$C$14))</f>
         <v/>
       </c>
@@ -7889,7 +7859,7 @@
           <t>Equity value attributable (30-Jun-2026)</t>
         </is>
       </c>
-      <c r="C59" s="27">
+      <c r="C59" s="28">
         <f>C48+SUM(C52:C58)</f>
         <v/>
       </c>
@@ -7900,7 +7870,7 @@
           <t>Fair value per share at 30-Jun-2026</t>
         </is>
       </c>
-      <c r="C60" s="23">
+      <c r="C60" s="24">
         <f>C59/Assumptions!$C$5</f>
         <v/>
       </c>
@@ -7911,7 +7881,7 @@
           <t>Anchor accretion (1+Ke)^(38/365)</t>
         </is>
       </c>
-      <c r="C61" s="29">
+      <c r="C61" s="30">
         <f>(1+C30)^(Assumptions!$C$68/365)</f>
         <v/>
       </c>
@@ -7922,7 +7892,7 @@
           <t>Fair value per share at the 7-Aug-2026 anchor</t>
         </is>
       </c>
-      <c r="C62" s="23">
+      <c r="C62" s="24">
         <f>C60*C61</f>
         <v/>
       </c>
@@ -8051,35 +8021,35 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
+      <c r="B5" s="21" t="n">
         <v>994.293</v>
       </c>
-      <c r="C5" s="19" t="n">
+      <c r="C5" s="21" t="n">
         <v>6511.182</v>
       </c>
-      <c r="D5" s="19" t="n">
+      <c r="D5" s="21" t="n">
         <v>13828.869</v>
       </c>
-      <c r="E5" s="19" t="n">
+      <c r="E5" s="21" t="n">
         <v>9188.304</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="20">
         <f>DCF!B5</f>
         <v/>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="20">
         <f>DCF!C5</f>
         <v/>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="20">
         <f>DCF!D5</f>
         <v/>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="20">
         <f>DCF!E5</f>
         <v/>
       </c>
-      <c r="J5" s="18">
+      <c r="J5" s="20">
         <f>DCF!F5</f>
         <v/>
       </c>
@@ -8090,35 +8060,35 @@
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
+      <c r="B6" s="21" t="n">
         <v>599.559</v>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="21" t="n">
         <v>2316.507</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="21" t="n">
         <v>5025.259</v>
       </c>
-      <c r="E6" s="19" t="n">
+      <c r="E6" s="21" t="n">
         <v>3201.275</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="20">
         <f>DCF!B6</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="20">
         <f>DCF!C6</f>
         <v/>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="20">
         <f>DCF!D6</f>
         <v/>
       </c>
-      <c r="I6" s="18">
+      <c r="I6" s="20">
         <f>DCF!E6</f>
         <v/>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="20">
         <f>DCF!F6</f>
         <v/>
       </c>
@@ -8129,32 +8099,32 @@
           <t>EBITDA (house)</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="21" t="n">
         <v>673.3530000000001</v>
       </c>
-      <c r="C7" s="19" t="n">
+      <c r="C7" s="21" t="n">
         <v>9794.941999999999</v>
       </c>
-      <c r="D7" s="19" t="n">
+      <c r="D7" s="21" t="n">
         <v>4895.552000000001</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="20">
         <f>DCF!B13</f>
         <v/>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="20">
         <f>DCF!C13</f>
         <v/>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="20">
         <f>DCF!D13</f>
         <v/>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="20">
         <f>DCF!E13</f>
         <v/>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="20">
         <f>DCF!F13</f>
         <v/>
       </c>
@@ -8165,35 +8135,35 @@
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="9">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="9">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="9">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="9">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="9">
         <f>J7/J5</f>
         <v/>
       </c>
@@ -8204,32 +8174,32 @@
           <t>Depreciation &amp; amortisation</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="21" t="n">
         <v>27.719</v>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="21" t="n">
         <v>265.122</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="21" t="n">
         <v>610.4829999999999</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="20">
         <f>DCF!B12</f>
         <v/>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="20">
         <f>DCF!C12</f>
         <v/>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="20">
         <f>DCF!D12</f>
         <v/>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="20">
         <f>DCF!E12</f>
         <v/>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="20">
         <f>DCF!F12</f>
         <v/>
       </c>
@@ -8240,35 +8210,35 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="19">
         <f>B7-B9</f>
         <v/>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="19">
         <f>C7-C9</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="19">
         <f>D7-D9</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="19">
         <f>F7-F9</f>
         <v/>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="19">
         <f>G7-G9</f>
         <v/>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="19">
         <f>H7-H9</f>
         <v/>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="19">
         <f>I7-I9</f>
         <v/>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="19">
         <f>J7-J9</f>
         <v/>
       </c>
@@ -8279,32 +8249,32 @@
           <t>Net finance result</t>
         </is>
       </c>
-      <c r="B11" s="19" t="n">
+      <c r="B11" s="21" t="n">
         <v>8.518000000000001</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="21" t="n">
         <v>-156.667</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="21" t="n">
         <v>-127.466</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="19">
         <f>(Assumptions!$C$52*'Balance Sheet'!E9-(DCF!$C$31*(Assumptions!$C$10+Assumptions!$C$51)/2+Assumptions!$C$53))*0.5</f>
         <v/>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="19">
         <f>(Assumptions!$C$52*'Balance Sheet'!F9-(DCF!$C$31*(Assumptions!$C$51+Assumptions!$D$51)/2+Assumptions!$C$53))*1.0</f>
         <v/>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="19">
         <f>(Assumptions!$C$52*'Balance Sheet'!G9-(DCF!$C$31*(Assumptions!$D$51+Assumptions!$E$51)/2+Assumptions!$C$53))*1.0</f>
         <v/>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="19">
         <f>(Assumptions!$C$52*'Balance Sheet'!H9-(DCF!$C$31*(Assumptions!$E$51+Assumptions!$F$51)/2+Assumptions!$C$53))*1.0</f>
         <v/>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="19">
         <f>(Assumptions!$C$52*'Balance Sheet'!I9-(DCF!$C$31*(Assumptions!$F$51+Assumptions!$G$51)/2+Assumptions!$C$53))*1.0</f>
         <v/>
       </c>
@@ -8315,32 +8285,32 @@
           <t>Associates &amp; JVs</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="21" t="n">
         <v>-0.697</v>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="21" t="n">
         <v>115.114</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="21" t="n">
         <v>263.592</v>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="20">
         <f>Assumptions!$C$50</f>
         <v/>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="20">
         <f>Assumptions!$D$50</f>
         <v/>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="20">
         <f>Assumptions!$E$50</f>
         <v/>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="20">
         <f>Assumptions!$F$50</f>
         <v/>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="20">
         <f>Assumptions!$G$50</f>
         <v/>
       </c>
@@ -8351,38 +8321,38 @@
           <t>Profit before tax</t>
         </is>
       </c>
-      <c r="B13" s="17">
+      <c r="B13" s="19">
         <f>B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="19">
         <f>C10+C11+C12</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="19">
         <f>D10+D11+D12</f>
         <v/>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="21" t="n">
         <v>2601.227</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="19">
         <f>F10+F11+F12</f>
         <v/>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="19">
         <f>G10+G11+G12</f>
         <v/>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="19">
         <f>H10+H11+H12</f>
         <v/>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="19">
         <f>I10+I11+I12</f>
         <v/>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="19">
         <f>J10+J11+J12</f>
         <v/>
       </c>
@@ -8393,35 +8363,35 @@
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B14" s="19" t="n">
+      <c r="B14" s="21" t="n">
         <v>-79.504</v>
       </c>
-      <c r="C14" s="19" t="n">
+      <c r="C14" s="21" t="n">
         <v>-98.815</v>
       </c>
-      <c r="D14" s="19" t="n">
+      <c r="D14" s="21" t="n">
         <v>-495.49</v>
       </c>
-      <c r="E14" s="19" t="n">
+      <c r="E14" s="21" t="n">
         <v>-401.202</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="19">
         <f>-F13*Assumptions!$C$48</f>
         <v/>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="19">
         <f>-G13*Assumptions!$C$48</f>
         <v/>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="19">
         <f>-H13*Assumptions!$C$48</f>
         <v/>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="19">
         <f>-I13*Assumptions!$C$48</f>
         <v/>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="19">
         <f>-J13*Assumptions!$C$48</f>
         <v/>
       </c>
@@ -8432,38 +8402,38 @@
           <t>Profit for the year</t>
         </is>
       </c>
-      <c r="B15" s="17">
+      <c r="B15" s="19">
         <f>B13+B14</f>
         <v/>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="19">
         <f>C13+C14</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="19">
         <f>D13+D14</f>
         <v/>
       </c>
-      <c r="E15" s="19" t="n">
+      <c r="E15" s="21" t="n">
         <v>2202.138</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="19">
         <f>F13+F14</f>
         <v/>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="19">
         <f>G13+G14</f>
         <v/>
       </c>
-      <c r="H15" s="17">
+      <c r="H15" s="19">
         <f>H13+H14</f>
         <v/>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="19">
         <f>I13+I14</f>
         <v/>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="19">
         <f>J13+J14</f>
         <v/>
       </c>
@@ -8474,35 +8444,35 @@
           <t>Non-controlling interests</t>
         </is>
       </c>
-      <c r="B16" s="19" t="n">
+      <c r="B16" s="21" t="n">
         <v>112.682</v>
       </c>
-      <c r="C16" s="19" t="n">
+      <c r="C16" s="21" t="n">
         <v>-33.7390000000014</v>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="21" t="n">
         <v>-94.39699999999993</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="21" t="n">
         <v>39.17200000000003</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F16" s="19">
         <f>F15*Assumptions!$C$49</f>
         <v/>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="19">
         <f>G15*Assumptions!$C$49</f>
         <v/>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="19">
         <f>H15*Assumptions!$C$49</f>
         <v/>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="19">
         <f>I15*Assumptions!$C$49</f>
         <v/>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="19">
         <f>J15*Assumptions!$C$49</f>
         <v/>
       </c>
@@ -8513,38 +8483,38 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="28">
         <f>B15-B16</f>
         <v/>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="28">
         <f>C15-C16</f>
         <v/>
       </c>
-      <c r="D17" s="27">
+      <c r="D17" s="28">
         <f>D15-D16</f>
         <v/>
       </c>
-      <c r="E17" s="33" t="n">
+      <c r="E17" s="34" t="n">
         <v>2162.966</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <f>F15-F16</f>
         <v/>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="28">
         <f>G15-G16</f>
         <v/>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="28">
         <f>H15-H16</f>
         <v/>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="28">
         <f>I15-I16</f>
         <v/>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="28">
         <f>J15-J16</f>
         <v/>
       </c>

--- a/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
+++ b/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
@@ -4160,7 +4160,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Weighted central (links to Summary)</t>
+          <t>THE CENTRAL — the cash-flow lens (links to Summary)</t>
         </is>
       </c>
       <c r="B14" s="13" t="n"/>

--- a/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
+++ b/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
@@ -146,11 +146,11 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1331,35 +1331,35 @@
           <t>Net debt / EBITDA</t>
         </is>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <f>(B12-B9)/673.3530000000001</f>
         <v/>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <f>(C12-C9)/9794.942</f>
         <v/>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <f>(D12-D9)/4895.552000000001</f>
         <v/>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <f>(F12-F9)/DCF!B13</f>
         <v/>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="30">
         <f>(G12-G9)/DCF!C13</f>
         <v/>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="30">
         <f>(H12-H9)/DCF!D13</f>
         <v/>
       </c>
-      <c r="I16" s="29">
+      <c r="I16" s="30">
         <f>(I12-I9)/DCF!E13</f>
         <v/>
       </c>
-      <c r="J16" s="29">
+      <c r="J16" s="30">
         <f>(J12-J9)/DCF!F13</f>
         <v/>
       </c>
@@ -2430,27 +2430,27 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
           <t>1.5%</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>2.0%</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>2.5%</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>3.0%</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>3.5%</t>
         </is>
       </c>
     </row>
@@ -2461,19 +2461,19 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>4.001441345629771</v>
+        <v>3.998811777954289</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>3.95946283254583</v>
+        <v>4.149389486489888</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>3.910344772050745</v>
+        <v>4.316584776332813</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>3.852748308118624</v>
+        <v>4.503330555390875</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3.784977502145205</v>
+        <v>4.713293063103003</v>
       </c>
     </row>
     <row r="6">
@@ -2483,19 +2483,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3.816186596964378</v>
+        <v>3.819788937699936</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>3.770181264157251</v>
+        <v>3.955006419928874</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.716987369055611</v>
+        <v>4.104411385994227</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3.655330156427179</v>
+        <v>4.270379302512826</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3.583614530716187</v>
+        <v>4.455847294724377</v>
       </c>
     </row>
     <row r="7">
@@ -2505,19 +2505,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>3.647209655008153</v>
+        <v>3.655824034516262</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>3.598302686890794</v>
+        <v>3.777750701924261</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3.542281748960128</v>
+        <v>3.911868712055091</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>3.47795036510495</v>
+        <v>4.060119639246211</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.403827815125312</v>
+        <v>4.224880454174783</v>
       </c>
     </row>
     <row r="8">
@@ -2527,19 +2527,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3.492450167113339</v>
+        <v>3.505094048591718</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.441519430814956</v>
+        <v>3.615453252943709</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.383630639503766</v>
+        <v>3.736350583564485</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3.317670925679249</v>
+        <v>3.869386193392378</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3.242276735048415</v>
+        <v>4.016501472142912</v>
       </c>
     </row>
     <row r="9">
@@ -2549,19 +2549,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.350181916662894</v>
+        <v>3.366059133168182</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.297915314030119</v>
+        <v>3.466296795192872</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3.238898679586645</v>
+        <v>3.575693042557749</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3.172102882509173</v>
+        <v>3.695576689904598</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3.096278384669553</v>
+        <v>3.827546678820739</v>
       </c>
     </row>
     <row r="11">
@@ -2603,19 +2603,19 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>5.59677097746544</v>
+        <v>6.123576759895837</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>4.332789993007912</v>
+        <v>4.776653374199568</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>3.542281748960128</v>
+        <v>3.911868712055091</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3.000067693883474</v>
+        <v>3.309509351127527</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>2.599030949816489</v>
+        <v>2.865813477125984</v>
       </c>
     </row>
     <row r="14">
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>3.236966465098836</v>
+        <v>3.527596574685213</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>3.389624107029481</v>
+        <v>3.719732643370151</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3.542281748960128</v>
+        <v>3.911868712055091</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>3.694939390890774</v>
+        <v>4.104004780740029</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>3.847597032821422</v>
+        <v>4.296140849424967</v>
       </c>
     </row>
     <row r="17">
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>3.199828427616535</v>
+        <v>3.513717901917142</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>3.383396312468598</v>
+        <v>3.728270212983312</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>3.542281748960128</v>
+        <v>3.911868712055091</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>3.679158184336495</v>
+        <v>4.067969792830735</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>3.796504953962525</v>
+        <v>4.199774963637052</v>
       </c>
     </row>
     <row r="20">
@@ -2765,19 +2765,19 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>2.827625020137998</v>
+        <v>2.986435726741846</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>3.185238080509545</v>
+        <v>3.449152219398469</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3.542281748960128</v>
+        <v>3.911868712055091</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>3.899325417410711</v>
+        <v>4.374585204711712</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>4.256369085861295</v>
+        <v>4.837301697368336</v>
       </c>
     </row>
     <row r="23">
@@ -2819,19 +2819,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>3.306873046398663</v>
+        <v>3.676460009493625</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>3.424577397679395</v>
+        <v>3.794164360774358</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>3.542281748960128</v>
+        <v>3.911868712055091</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3.65998610024086</v>
+        <v>4.029573063335822</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>3.777690451521593</v>
+        <v>4.147277414616555</v>
       </c>
     </row>
     <row r="26">
@@ -2873,19 +2873,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>3.856689481389984</v>
+        <v>4.273272416773525</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>3.699485615175056</v>
+        <v>4.092570564414308</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3.542281748960128</v>
+        <v>3.911868712055091</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>3.3850778827452</v>
+        <v>3.731166859695873</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>3.227874016530273</v>
+        <v>3.550465007336656</v>
       </c>
     </row>
     <row r="29">
@@ -2927,19 +2927,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>3.542281748960128</v>
+        <v>3.911868712055091</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>3.383630639503766</v>
+        <v>3.736350583564485</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>3.238898679586645</v>
+        <v>3.575693042557749</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3.106314064026041</v>
+        <v>3.42808434756411</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2.984394294784054</v>
+        <v>3.29199609699272</v>
       </c>
     </row>
   </sheetData>
@@ -3217,15 +3217,15 @@
           <t>P/E at spot (full years)</t>
         </is>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>Assumptions!$C$4/B5</f>
         <v/>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <f>Assumptions!$C$4/C5</f>
         <v/>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <f>Assumptions!$C$4/D5</f>
         <v/>
       </c>
@@ -3239,19 +3239,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="30">
         <f>Assumptions!$C$4/G5</f>
         <v/>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="30">
         <f>Assumptions!$C$4/H5</f>
         <v/>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="30">
         <f>Assumptions!$C$4/I5</f>
         <v/>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="30">
         <f>Assumptions!$C$4/J5</f>
         <v/>
       </c>
@@ -3262,39 +3262,39 @@
           <t>P/B at spot</t>
         </is>
       </c>
-      <c r="B10" s="29">
+      <c r="B10" s="30">
         <f>Assumptions!$C$4/B6</f>
         <v/>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>Assumptions!$C$4/C6</f>
         <v/>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="30">
         <f>Assumptions!$C$4/D6</f>
         <v/>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <f>Assumptions!$C$4/E6</f>
         <v/>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>Assumptions!$C$4/F6</f>
         <v/>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>Assumptions!$C$4/G6</f>
         <v/>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <f>Assumptions!$C$4/H6</f>
         <v/>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="30">
         <f>Assumptions!$C$4/I6</f>
         <v/>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="30">
         <f>Assumptions!$C$4/J6</f>
         <v/>
       </c>
@@ -3400,7 +3400,7 @@
       <c r="E5" s="21" t="n">
         <v>7548</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <f>D5/E5</f>
         <v/>
       </c>
@@ -3427,7 +3427,7 @@
       <c r="E6" s="21" t="n">
         <v>17599</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <f>D6/E6</f>
         <v/>
       </c>
@@ -3454,7 +3454,7 @@
       <c r="E7" s="21" t="n">
         <v>11316</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <f>D7/E7</f>
         <v/>
       </c>
@@ -3481,10 +3481,10 @@
         <v/>
       </c>
       <c r="E8" s="20">
-        <f>Assumptions!$C$71</f>
-        <v/>
-      </c>
-      <c r="F8" s="29">
+        <f>Assumptions!$C$74</f>
+        <v/>
+      </c>
+      <c r="F8" s="30">
         <f>D8/E8</f>
         <v/>
       </c>
@@ -3598,14 +3598,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2.643232316556594</v>
+        <v>2.746942674345072</v>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C62</f>
+        <f>DCF!C68</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>4.13375247645742</v>
+        <v>4.683860662745367</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -3757,11 +3757,11 @@
         </is>
       </c>
       <c r="C12" s="8">
-        <f>DCF!C62</f>
+        <f>DCF!C68</f>
         <v/>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.643232316556594</v>
+        <v>2.746942674345072</v>
       </c>
     </row>
     <row r="13">
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="C13" s="17">
-        <f>DCF!C49</f>
+        <f>DCF!C55</f>
         <v/>
       </c>
     </row>
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2.478745616179524</v>
+        <v>2.582455973968002</v>
       </c>
     </row>
     <row r="15">
@@ -3892,11 +3892,11 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal growth (inflation × real growth)</t>
         </is>
       </c>
       <c r="C25" s="22">
-        <f>Assumptions!$C$66</f>
+        <f>(1+Assumptions!$C$67)*(1+Assumptions!$C$66)-1</f>
         <v/>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
         </is>
       </c>
       <c r="C5" s="8">
-        <f>DCF!C62</f>
+        <f>DCF!C68</f>
         <v/>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>2.643232316556594</v>
+        <v>2.746942674345072</v>
       </c>
     </row>
     <row r="7">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4.13375247645742</v>
+        <v>4.683860662745367</v>
       </c>
     </row>
     <row r="8">
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2.827564759210456</v>
+        <v>3.117266498324851</v>
       </c>
     </row>
     <row r="9">
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.771628430049033</v>
+        <v>4.141215393143995</v>
       </c>
     </row>
     <row r="10">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>0.02693414991240069</v>
+        <v>0.04045008173003765</v>
       </c>
     </row>
     <row r="18">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>2.478745616179524</v>
+        <v>2.582455973968002</v>
       </c>
     </row>
     <row r="21">
@@ -4268,7 +4268,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -5190,290 +5190,321 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth</t>
+          <t>Terminal REAL growth (stated, not derived)</t>
         </is>
       </c>
       <c r="C66" s="23" t="n">
-        <v>0.025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
+          <t>Terminal inflation — UAE house macro path</t>
         </is>
       </c>
       <c r="C67" s="23" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>Days from the 30-Jun-2026 valuation date to the 7-Aug anchor</t>
+          <t>Longest useful life the company discloses (years)</t>
         </is>
       </c>
       <c r="C68" s="21" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>FY2025 disclosed anchors (audited, pasted)</t>
-        </is>
-      </c>
-      <c r="B69" s="13" t="n"/>
-      <c r="C69" s="13" t="n"/>
-      <c r="D69" s="13" t="n"/>
-      <c r="E69" s="13" t="n"/>
-      <c r="F69" s="13" t="n"/>
-      <c r="G69" s="13" t="n"/>
-      <c r="H69" s="13" t="n"/>
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Invested capital per unit of real growth, at terminal revenue (AED mn)</t>
+        </is>
+      </c>
+      <c r="C69" s="21" t="n">
+        <v>12501.28648199712</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>FY2025 profit for the year (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C70" s="21" t="n">
-        <v>3925.705</v>
+          <t>Terminal growth = (1 + inflation) × (1 + real growth) − 1</t>
+        </is>
+      </c>
+      <c r="C70" s="27">
+        <f>(1+$C$67)*(1+$C$66)-1</f>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>FY2025 attributable profit (AED mn, disclosed)</t>
+          <t>Days from the 30-Jun-2026 valuation date to the 7-Aug anchor</t>
         </is>
       </c>
       <c r="C71" s="21" t="n">
-        <v>4020.102</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>FY2025 EBITDA, house basis = EBIT + D&amp;A (AED mn)</t>
-        </is>
-      </c>
-      <c r="C72" s="21" t="n">
-        <v>4895.552000000001</v>
-      </c>
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>FY2025 disclosed anchors (audited, pasted)</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="n"/>
+      <c r="C72" s="13" t="n"/>
+      <c r="D72" s="13" t="n"/>
+      <c r="E72" s="13" t="n"/>
+      <c r="F72" s="13" t="n"/>
+      <c r="G72" s="13" t="n"/>
+      <c r="H72" s="13" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>FY2025 net debt, strict basis (AED mn)</t>
+          <t>FY2025 profit for the year (AED mn, disclosed)</t>
         </is>
       </c>
       <c r="C73" s="21" t="n">
-        <v>-5852.901</v>
+        <v>3925.705</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="10" t="inlineStr">
-        <is>
-          <t>Lens settings</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n"/>
-      <c r="C74" s="13" t="n"/>
-      <c r="D74" s="13" t="n"/>
-      <c r="E74" s="13" t="n"/>
-      <c r="F74" s="13" t="n"/>
-      <c r="G74" s="13" t="n"/>
-      <c r="H74" s="13" t="n"/>
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>FY2025 attributable profit (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C74" s="21" t="n">
+        <v>4020.102</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>Justified price/earnings (FY2026E attributable)</t>
-        </is>
-      </c>
-      <c r="C75" s="26" t="n">
-        <v>7.5</v>
+          <t>FY2025 EBITDA, house basis = EBIT + D&amp;A (AED mn)</t>
+        </is>
+      </c>
+      <c r="C75" s="21" t="n">
+        <v>4895.552000000001</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>EV/EBITDA cross-check multiple (house judgement, unanchored)</t>
-        </is>
-      </c>
-      <c r="C76" s="26" t="n">
-        <v>7</v>
+          <t>FY2025 net debt, strict basis (AED mn)</t>
+        </is>
+      </c>
+      <c r="C76" s="21" t="n">
+        <v>-5852.901</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr">
-        <is>
-          <t>Through-cycle development sales (AED mn)</t>
-        </is>
-      </c>
-      <c r="C77" s="21" t="n">
-        <v>20000</v>
-      </c>
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>Lens settings</t>
+        </is>
+      </c>
+      <c r="B77" s="13" t="n"/>
+      <c r="C77" s="13" t="n"/>
+      <c r="D77" s="13" t="n"/>
+      <c r="E77" s="13" t="n"/>
+      <c r="F77" s="13" t="n"/>
+      <c r="G77" s="13" t="n"/>
+      <c r="H77" s="13" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>Through-cycle net margin on revenue</t>
-        </is>
-      </c>
-      <c r="C78" s="25" t="n">
-        <v>0.115</v>
+          <t>Justified price/earnings (FY2026E attributable)</t>
+        </is>
+      </c>
+      <c r="C78" s="26" t="n">
+        <v>7.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>Recurring-legs revenue base, FY2025 (AED mn, disclosed)</t>
-        </is>
-      </c>
-      <c r="C79" s="21" t="n">
-        <v>6455.178</v>
+          <t>EV/EBITDA cross-check multiple (house judgement, unanchored)</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>Through-cycle price/earnings</t>
-        </is>
-      </c>
-      <c r="C80" s="26" t="n">
-        <v>8.5</v>
+          <t>Through-cycle development sales (AED mn)</t>
+        </is>
+      </c>
+      <c r="C80" s="21" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>Sustainable return on equity</t>
+          <t>Through-cycle net margin on revenue</t>
         </is>
       </c>
       <c r="C81" s="25" t="n">
-        <v>0.075</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="10" t="inlineStr">
-        <is>
-          <t>Scenario driver vectors (engine re-run inputs, published for reproducibility — the pasted scenario outputs use exactly these)</t>
-        </is>
-      </c>
-      <c r="B82" s="13" t="n"/>
-      <c r="C82" s="13" t="n"/>
-      <c r="D82" s="13" t="n"/>
-      <c r="E82" s="13" t="n"/>
-      <c r="F82" s="13" t="n"/>
-      <c r="G82" s="13" t="n"/>
-      <c r="H82" s="13" t="n"/>
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Recurring-legs revenue base, FY2025 (AED mn, disclosed)</t>
+        </is>
+      </c>
+      <c r="C82" s="21" t="n">
+        <v>6455.178</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>scenario: run-off new development sales</t>
-        </is>
-      </c>
-      <c r="C83" s="21" t="n">
-        <v>8000</v>
-      </c>
-      <c r="D83" s="21" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E83" s="21" t="n">
-        <v>11000</v>
-      </c>
-      <c r="F83" s="21" t="n">
-        <v>9000</v>
-      </c>
-      <c r="G83" s="21" t="n">
-        <v>8000</v>
+          <t>Through-cycle price/earnings</t>
+        </is>
+      </c>
+      <c r="C83" s="26" t="n">
+        <v>8.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>scenario: run-off development margin</t>
+          <t>Sustainable return on equity</t>
         </is>
       </c>
       <c r="C84" s="25" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D84" s="25" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E84" s="25" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="F84" s="25" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="G84" s="25" t="n">
-        <v>0.35</v>
+        <v>0.075</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="6" t="inlineStr">
-        <is>
-          <t>scenario: growth-hold new development sales</t>
-        </is>
-      </c>
-      <c r="C85" s="21" t="n">
-        <v>15000</v>
-      </c>
-      <c r="D85" s="21" t="n">
-        <v>34000</v>
-      </c>
-      <c r="E85" s="21" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F85" s="21" t="n">
-        <v>34000</v>
-      </c>
-      <c r="G85" s="21" t="n">
-        <v>34000</v>
-      </c>
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Scenario driver vectors (engine re-run inputs, published for reproducibility — the pasted scenario outputs use exactly these)</t>
+        </is>
+      </c>
+      <c r="B85" s="13" t="n"/>
+      <c r="C85" s="13" t="n"/>
+      <c r="D85" s="13" t="n"/>
+      <c r="E85" s="13" t="n"/>
+      <c r="F85" s="13" t="n"/>
+      <c r="G85" s="13" t="n"/>
+      <c r="H85" s="13" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>scenario: growth-hold development margin</t>
-        </is>
-      </c>
-      <c r="C86" s="25" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D86" s="25" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E86" s="25" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="F86" s="25" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G86" s="25" t="n">
-        <v>0.4</v>
+          <t>scenario: run-off new development sales</t>
+        </is>
+      </c>
+      <c r="C86" s="21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D86" s="21" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E86" s="21" t="n">
+        <v>11000</v>
+      </c>
+      <c r="F86" s="21" t="n">
+        <v>9000</v>
+      </c>
+      <c r="G86" s="21" t="n">
+        <v>8000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>scenario: Egypt stress — non-UAE revenue share (note 5)</t>
+          <t>scenario: run-off development margin</t>
         </is>
       </c>
       <c r="C87" s="25" t="n">
-        <v>0.170797409390457</v>
+        <v>0.4</v>
+      </c>
+      <c r="D87" s="25" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E87" s="25" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F87" s="25" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="G87" s="25" t="n">
+        <v>0.35</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
+          <t>scenario: growth-hold new development sales</t>
+        </is>
+      </c>
+      <c r="C88" s="21" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D88" s="21" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E88" s="21" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F88" s="21" t="n">
+        <v>34000</v>
+      </c>
+      <c r="G88" s="21" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>scenario: growth-hold development margin</t>
+        </is>
+      </c>
+      <c r="C89" s="25" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="D89" s="25" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E89" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F89" s="25" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="G89" s="25" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>scenario: Egypt stress — non-UAE revenue share (note 5)</t>
+        </is>
+      </c>
+      <c r="C90" s="25" t="n">
+        <v>0.170797409390457</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
           <t>scenario: Egypt country risk premium (Damodaran)</t>
         </is>
       </c>
-      <c r="C88" s="23" t="n">
+      <c r="C91" s="23" t="n">
         <v>0.09710000000000001</v>
       </c>
     </row>
@@ -5556,7 +5587,7 @@
         <v/>
       </c>
       <c r="C6" s="19">
-        <f>MAX(B6,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
+        <f>MAX(B6,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C54</f>
         <v/>
       </c>
     </row>
@@ -5571,7 +5602,7 @@
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>MAX(B7,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
+        <f>MAX(B7,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C54</f>
         <v/>
       </c>
     </row>
@@ -5586,7 +5617,7 @@
         <v/>
       </c>
       <c r="C8" s="19">
-        <f>MAX(B8,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
+        <f>MAX(B8,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C54</f>
         <v/>
       </c>
     </row>
@@ -5601,7 +5632,7 @@
         <v/>
       </c>
       <c r="C9" s="19">
-        <f>MAX(B9,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C48</f>
+        <f>MAX(B9,0)/(MAX(B$6,0)+MAX(B$7,0)+MAX(B$8,0)+MAX(B$9,0))*DCF!C54</f>
         <v/>
       </c>
     </row>
@@ -5612,8 +5643,8 @@
         </is>
       </c>
       <c r="B10" s="13" t="n"/>
-      <c r="C10" s="27">
-        <f>DCF!C48</f>
+      <c r="C10" s="28">
+        <f>DCF!C54</f>
         <v/>
       </c>
       <c r="D10" s="13" t="n"/>
@@ -5627,7 +5658,7 @@
         </is>
       </c>
       <c r="C11" s="9">
-        <f>DCF!C49</f>
+        <f>DCF!C55</f>
         <v/>
       </c>
     </row>
@@ -5693,7 +5724,7 @@
         </is>
       </c>
       <c r="C17" s="20">
-        <f>DCF!C58</f>
+        <f>DCF!C64</f>
         <v/>
       </c>
     </row>
@@ -5704,7 +5735,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n"/>
-      <c r="C18" s="27">
+      <c r="C18" s="28">
         <f>C10+SUM(C12:C17)</f>
         <v/>
       </c>
@@ -5730,7 +5761,7 @@
         </is>
       </c>
       <c r="C20" s="24">
-        <f>C19*DCF!C61</f>
+        <f>C19*DCF!C67</f>
         <v/>
       </c>
     </row>
@@ -5741,7 +5772,7 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>3.556285567996332</v>
+        <v>3.933415122174865</v>
       </c>
     </row>
   </sheetData>
@@ -5932,11 +5963,11 @@
           <t>Group FY2025</t>
         </is>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="28">
         <f>SUM(B5:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="28">
         <f>SUM(C5:C9)</f>
         <v/>
       </c>
@@ -6119,23 +6150,23 @@
           <t>Real Estate Development revenue</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="29">
         <f>B15+B17</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>C15+C17</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>D15+D17</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f>E15+E17</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f>F15+F17</f>
         <v/>
       </c>
@@ -6313,23 +6344,23 @@
           <t>Group revenue</t>
         </is>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="29">
         <f>SUM(B21:B25)</f>
         <v/>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="29">
         <f>SUM(C21:C25)</f>
         <v/>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="29">
         <f>SUM(D21:D25)</f>
         <v/>
       </c>
-      <c r="E26" s="28">
+      <c r="E26" s="29">
         <f>SUM(E21:E25)</f>
         <v/>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="29">
         <f>SUM(F21:F25)</f>
         <v/>
       </c>
@@ -6507,23 +6538,23 @@
           <t>Group gross profit</t>
         </is>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="29">
         <f>SUM(B29:B33)</f>
         <v/>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="29">
         <f>SUM(C29:C33)</f>
         <v/>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="29">
         <f>SUM(D29:D33)</f>
         <v/>
       </c>
-      <c r="E34" s="28">
+      <c r="E34" s="29">
         <f>SUM(E29:E33)</f>
         <v/>
       </c>
-      <c r="F34" s="28">
+      <c r="F34" s="29">
         <f>SUM(F29:F33)</f>
         <v/>
       </c>
@@ -6628,7 +6659,7 @@
         </is>
       </c>
       <c r="C6" s="16">
-        <f>Assumptions!$C$75*C5/Assumptions!$C$5</f>
+        <f>Assumptions!$C$78*C5/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
@@ -6650,7 +6681,7 @@
         </is>
       </c>
       <c r="C8" s="16">
-        <f>(Assumptions!$C$76*C7+Assumptions!$C$8-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-MAX(Assumptions!$C$14,0.02*(Assumptions!$C$76*C7+Assumptions!$C$8-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-Assumptions!$C$14)))/Assumptions!$C$5</f>
+        <f>(Assumptions!$C$79*C7+Assumptions!$C$8-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-MAX(Assumptions!$C$14,0.02*(Assumptions!$C$79*C7+Assumptions!$C$8-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-Assumptions!$C$14)))/Assumptions!$C$5</f>
         <v/>
       </c>
     </row>
@@ -6677,11 +6708,11 @@
         </is>
       </c>
       <c r="C12" s="16">
-        <f>C11*4.73/Assumptions!$C$75</f>
+        <f>C11*4.73/Assumptions!$C$78</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>C11*8.1/Assumptions!$C$75</f>
+        <f>C11*8.1/Assumptions!$C$78</f>
         <v/>
       </c>
     </row>
@@ -6703,8 +6734,8 @@
           <t>Trailing P/E on FY2025 attributable profit</t>
         </is>
       </c>
-      <c r="C15" s="29">
-        <f>DCF!C33/Assumptions!$C$71</f>
+      <c r="C15" s="30">
+        <f>DCF!C33/Assumptions!$C$74</f>
         <v/>
       </c>
     </row>
@@ -6714,8 +6745,8 @@
           <t>Trailing P/E on FY2025 group profit (dual-framed)</t>
         </is>
       </c>
-      <c r="C16" s="29">
-        <f>DCF!C33/Assumptions!$C$70</f>
+      <c r="C16" s="30">
+        <f>DCF!C33/Assumptions!$C$73</f>
         <v/>
       </c>
     </row>
@@ -6725,8 +6756,8 @@
           <t>Trailing EV/EBITDA (mktcap + FY2025 strict net debt over house EBITDA)</t>
         </is>
       </c>
-      <c r="C17" s="29">
-        <f>(DCF!C33+Assumptions!$C$73)/Assumptions!$C$72</f>
+      <c r="C17" s="30">
+        <f>(DCF!C33+Assumptions!$C$76)/Assumptions!$C$75</f>
         <v/>
       </c>
     </row>
@@ -6749,7 +6780,7 @@
         </is>
       </c>
       <c r="C20" s="19">
-        <f>Assumptions!$C$77*0.85+Assumptions!$C$79*1.15</f>
+        <f>Assumptions!$C$80*0.85+Assumptions!$C$82*1.15</f>
         <v/>
       </c>
     </row>
@@ -6760,7 +6791,7 @@
         </is>
       </c>
       <c r="C21" s="17">
-        <f>Assumptions!$C$78</f>
+        <f>Assumptions!$C$81</f>
         <v/>
       </c>
     </row>
@@ -6793,7 +6824,7 @@
         </is>
       </c>
       <c r="C28" s="24">
-        <f>C23*Assumptions!$C$80</f>
+        <f>C23*Assumptions!$C$83</f>
         <v/>
       </c>
       <c r="E28" s="16">
@@ -6834,8 +6865,8 @@
           <t>Justified P/B = (ROE − g)/(Ke − g)</t>
         </is>
       </c>
-      <c r="C32" s="29">
-        <f>(Assumptions!$C$81-Assumptions!$C$66)/(DCF!C30-Assumptions!$C$66)</f>
+      <c r="C32" s="30">
+        <f>(Assumptions!$C$84-Assumptions!$C$70)/(DCF!C30-Assumptions!$C$70)</f>
         <v/>
       </c>
     </row>
@@ -6846,15 +6877,15 @@
         </is>
       </c>
       <c r="C36" s="24">
-        <f>C31*C32*DCF!C61</f>
+        <f>C31*C32*DCF!C67</f>
         <v/>
       </c>
       <c r="E36" s="16">
-        <f>C31*((0.055-Assumptions!$C$66)/(DCF!C30-Assumptions!$C$66))*DCF!C61</f>
+        <f>C31*((0.055-Assumptions!$C$70)/(DCF!C30-Assumptions!$C$70))*DCF!C67</f>
         <v/>
       </c>
       <c r="F36" s="16">
-        <f>C31*((0.095-Assumptions!$C$66)/(DCF!C30-Assumptions!$C$66))*DCF!C61</f>
+        <f>C31*((0.095-Assumptions!$C$70)/(DCF!C30-Assumptions!$C$70))*DCF!C67</f>
         <v/>
       </c>
     </row>
@@ -6869,7 +6900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7076,23 +7107,23 @@
           <t>EBIT (post-D&amp;A, ex-fair-value items)</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="29">
         <f>SUM(B6:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <f>SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <f>SUM(D6:D9)</f>
         <v/>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <f>SUM(E6:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <f>SUM(F6:F9)</f>
         <v/>
       </c>
@@ -7292,23 +7323,23 @@
           <t>Free cash flow to firm</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="29">
         <f>SUM(B14:B17)</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="29">
         <f>SUM(C14:C17)</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="29">
         <f>SUM(D14:D17)</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="29">
         <f>SUM(E14:E17)</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <f>SUM(F14:F17)</f>
         <v/>
       </c>
@@ -7319,23 +7350,23 @@
           <t>Discount factor (period-end from 30-Jun-2026)</t>
         </is>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>1/(1+$C$36)^0.5</f>
         <v/>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <f>1/(1+$C$36)^1.5</f>
         <v/>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <f>1/(1+$C$36)^2.5</f>
         <v/>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <f>1/(1+$C$36)^3.5</f>
         <v/>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <f>1/(1+$C$36)^4.5</f>
         <v/>
       </c>
@@ -7560,7 +7591,7 @@
           <t>Cost of equity Ke = rf* + β × ERP (β from the panel-proxy regression)</t>
         </is>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="27">
         <f>C29+Assumptions!$C$63*Assumptions!$C$62</f>
         <v/>
       </c>
@@ -7571,7 +7602,7 @@
           <t>Marginal cost of debt Kd = 6M EIBOR + margin</t>
         </is>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="27">
         <f>Assumptions!$C$64+Assumptions!$C$65</f>
         <v/>
       </c>
@@ -7582,7 +7613,7 @@
           <t>Kd after tax</t>
         </is>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="27">
         <f>C31*(1-Assumptions!$C$48)</f>
         <v/>
       </c>
@@ -7604,7 +7635,7 @@
           <t>Equity weight E/(E+D), debt at the 30-Jun-2026 book</t>
         </is>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="27">
         <f>C33/(C33+Assumptions!$C$10)</f>
         <v/>
       </c>
@@ -7615,7 +7646,7 @@
           <t>Debt weight D/(E+D)</t>
         </is>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="27">
         <f>1-C34</f>
         <v/>
       </c>
@@ -7637,7 +7668,7 @@
           <t>Terminal debt weight — DERIVED from the FY2030E balance sheet</t>
         </is>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="27">
         <f>'Balance Sheet'!J12/('Balance Sheet'!J12+'Balance Sheet'!J14+'Balance Sheet'!J15)</f>
         <v/>
       </c>
@@ -7656,7 +7687,7 @@
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>Terminal block — reinvestment derived</t>
+          <t>Terminal block — capital maintained at replacement cost over the disclosed asset life</t>
         </is>
       </c>
       <c r="B40" s="13" t="n"/>
@@ -7670,7 +7701,7 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Terminal growth g</t>
+          <t>Terminal REAL growth (stated)</t>
         </is>
       </c>
       <c r="C41" s="22">
@@ -7681,7 +7712,7 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Terminal return on invested capital</t>
+          <t>Terminal inflation — UAE house macro path</t>
         </is>
       </c>
       <c r="C42" s="22">
@@ -7692,11 +7723,11 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>Reinvestment rate = g / ROIC</t>
-        </is>
-      </c>
-      <c r="C43" s="31">
-        <f>C41/C42</f>
+          <t>Terminal growth g = (1+inflation)(1+real growth) − 1</t>
+        </is>
+      </c>
+      <c r="C43" s="27">
+        <f>(1+C42)*(1+C41)-1</f>
         <v/>
       </c>
     </row>
@@ -7707,213 +7738,279 @@
         </is>
       </c>
       <c r="C44" s="19">
-        <f>F14*(1+C41)</f>
+        <f>F14*(1+C43)</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Terminal value = NOPAT × (1−RR) / (WACCterm − g)</t>
+          <t>Plus book depreciation and amortisation, grown one year</t>
         </is>
       </c>
       <c r="C45" s="19">
-        <f>C44*(1-C43)/(C38-C41)</f>
+        <f>F12*(1+C43)</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>PV of terminal value (year-4.5 factor)</t>
+          <t>Less capital maintenance at replacement cost — book D&amp;A escalated over half the disclosed life</t>
         </is>
       </c>
       <c r="C46" s="19">
-        <f>C45*F19</f>
+        <f>-C45*(1+C42)^(Assumptions!$C$68/2)</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>PV of explicit periods</t>
+          <t>Less capital for REAL growth (real growth × capital per unit of growth)</t>
         </is>
       </c>
       <c r="C47" s="19">
-        <f>SUM(B20:F20)</f>
+        <f>-C41*Assumptions!$C$69</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Enterprise value</t>
-        </is>
-      </c>
-      <c r="C48" s="28">
-        <f>C46+C47</f>
+          <t>Less inflation on the working capital the business carries</t>
+        </is>
+      </c>
+      <c r="C48" s="19">
+        <f>-C42*37849.906247</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>Terminal value share of enterprise value</t>
-        </is>
-      </c>
-      <c r="C49" s="33">
-        <f>C46/C48</f>
+          <t>Terminal free cash flow</t>
+        </is>
+      </c>
+      <c r="C49" s="29">
+        <f>SUM(C44:C48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Terminal value = terminal free cash flow × (1+g) / (WACCterm − g)</t>
+        </is>
+      </c>
+      <c r="C50" s="19">
+        <f>C49*(1+C43)/(C38-C43)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="inlineStr">
-        <is>
-          <t>EV → equity bridge (30-Jun-2026, available-cash basis)</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="n"/>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
-      <c r="F51" s="13" t="n"/>
-      <c r="G51" s="13" t="n"/>
-      <c r="H51" s="13" t="n"/>
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Memo — the no-growth perpetuity at book depreciation (a diagnostic, not a bound)</t>
+        </is>
+      </c>
+      <c r="C51" s="19">
+        <f>C44/C38</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>+ Unrestricted (available) cash — disclosed</t>
-        </is>
-      </c>
-      <c r="C52" s="20">
-        <f>Assumptions!$C$8</f>
+          <t>PV of terminal value (year-4.5 factor)</t>
+        </is>
+      </c>
+      <c r="C52" s="19">
+        <f>C50*F19</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (project escrow/restricted cash of 3,703 is excluded: it funds completion of the backlog the DCF values)</t>
-        </is>
+          <t>PV of explicit periods</t>
+        </is>
+      </c>
+      <c r="C53" s="19">
+        <f>SUM(B20:F20)</f>
+        <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>− Gross debt incl. related-party loan</t>
-        </is>
-      </c>
-      <c r="C54" s="20">
-        <f>-Assumptions!$C$10</f>
+          <t>Enterprise value</t>
+        </is>
+      </c>
+      <c r="C54" s="29">
+        <f>C52+C53</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>− Lease liabilities</t>
-        </is>
-      </c>
-      <c r="C55" s="20">
-        <f>-Assumptions!$C$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>+ Associates &amp; JVs at carrying value</t>
-        </is>
-      </c>
-      <c r="C56" s="20">
-        <f>Assumptions!$C$12</f>
+          <t>Terminal value share of enterprise value</t>
+        </is>
+      </c>
+      <c r="C55" s="33">
+        <f>C52/C54</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>+ Investments in financial assets</t>
-        </is>
-      </c>
-      <c r="C57" s="20">
-        <f>Assumptions!$C$13</f>
-        <v/>
-      </c>
+      <c r="A57" s="10" t="inlineStr">
+        <is>
+          <t>EV → equity bridge (30-Jun-2026, available-cash basis)</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="n"/>
+      <c r="C57" s="13" t="n"/>
+      <c r="D57" s="13" t="n"/>
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="13" t="n"/>
+      <c r="G57" s="13" t="n"/>
+      <c r="H57" s="13" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>− Non-controlling interests, capitalised at share of equity value (MAX of book and 2%)</t>
-        </is>
-      </c>
-      <c r="C58" s="19">
-        <f>-MAX(Assumptions!$C$14,0.02*(C48+C52-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-Assumptions!$C$14))</f>
+          <t>+ Unrestricted (available) cash — disclosed</t>
+        </is>
+      </c>
+      <c r="C58" s="20">
+        <f>Assumptions!$C$8</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>Equity value attributable (30-Jun-2026)</t>
-        </is>
-      </c>
-      <c r="C59" s="28">
-        <f>C48+SUM(C52:C58)</f>
-        <v/>
+          <t xml:space="preserve">   (project escrow/restricted cash of 3,703 is excluded: it funds completion of the backlog the DCF values)</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Fair value per share at 30-Jun-2026</t>
-        </is>
-      </c>
-      <c r="C60" s="24">
-        <f>C59/Assumptions!$C$5</f>
+          <t>− Gross debt incl. related-party loan</t>
+        </is>
+      </c>
+      <c r="C60" s="20">
+        <f>-Assumptions!$C$10</f>
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Anchor accretion (1+Ke)^(38/365)</t>
-        </is>
-      </c>
-      <c r="C61" s="30">
-        <f>(1+C30)^(Assumptions!$C$68/365)</f>
+          <t>− Lease liabilities</t>
+        </is>
+      </c>
+      <c r="C61" s="20">
+        <f>-Assumptions!$C$11</f>
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>Fair value per share at the 7-Aug-2026 anchor</t>
-        </is>
-      </c>
-      <c r="C62" s="24">
-        <f>C60*C61</f>
+          <t>+ Associates &amp; JVs at carrying value</t>
+        </is>
+      </c>
+      <c r="C62" s="20">
+        <f>Assumptions!$C$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>+ Investments in financial assets</t>
+        </is>
+      </c>
+      <c r="C63" s="20">
+        <f>Assumptions!$C$13</f>
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
+          <t>− Non-controlling interests, capitalised at share of equity value (MAX of book and 2%)</t>
+        </is>
+      </c>
+      <c r="C64" s="19">
+        <f>-MAX(Assumptions!$C$14,0.02*(C54+C58-Assumptions!$C$10-Assumptions!$C$11+Assumptions!$C$12+Assumptions!$C$13-Assumptions!$C$14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Equity value attributable (30-Jun-2026)</t>
+        </is>
+      </c>
+      <c r="C65" s="29">
+        <f>C54+SUM(C58:C64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Fair value per share at 30-Jun-2026</t>
+        </is>
+      </c>
+      <c r="C66" s="24">
+        <f>C65/Assumptions!$C$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Anchor accretion (1+Ke)^(38/365)</t>
+        </is>
+      </c>
+      <c r="C67" s="31">
+        <f>(1+C30)^(Assumptions!$C$71/365)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Fair value per share at the 7-Aug-2026 anchor</t>
+        </is>
+      </c>
+      <c r="C68" s="24">
+        <f>C66*C67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
           <t>Alternatives (engine re-runs, pasted; driver vectors on Assumptions): run-off stress / growth-hold / Egypt stress / gross-cash basis</t>
         </is>
       </c>
-      <c r="C64" s="7" t="n">
-        <v>2.643232316556594</v>
-      </c>
-      <c r="D64" s="7" t="n">
-        <v>4.13375247645742</v>
-      </c>
-      <c r="E64" s="7" t="n">
-        <v>2.827564759210456</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>3.771628430049033</v>
+      <c r="C70" s="7" t="n">
+        <v>2.746942674345072</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>4.683860662745367</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>3.117266498324851</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>4.141215393143995</v>
       </c>
     </row>
   </sheetData>
@@ -8483,38 +8580,38 @@
           <t>Attributable profit</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="29">
         <f>B15-B16</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="29">
         <f>C15-C16</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="29">
         <f>D15-D16</f>
         <v/>
       </c>
       <c r="E17" s="34" t="n">
         <v>2162.966</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="29">
         <f>F15-F16</f>
         <v/>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="29">
         <f>G15-G16</f>
         <v/>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="29">
         <f>H15-H16</f>
         <v/>
       </c>
-      <c r="I17" s="28">
+      <c r="I17" s="29">
         <f>I15-I16</f>
         <v/>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="29">
         <f>J15-J16</f>
         <v/>
       </c>

--- a/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
+++ b/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
@@ -2461,19 +2461,19 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>3.998811777954289</v>
+        <v>3.971617869941458</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>4.149389486489888</v>
+        <v>4.106238914811883</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>4.316584776332813</v>
+        <v>4.255554770291383</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>4.503330555390875</v>
+        <v>4.422158986274013</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>4.713293063103003</v>
+        <v>4.609293592583864</v>
       </c>
     </row>
     <row r="6">
@@ -2483,19 +2483,19 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>3.819788937699936</v>
+        <v>3.794213818824098</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>3.955006419928874</v>
+        <v>3.914518214491936</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>4.104411385994227</v>
+        <v>4.0472934555231</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>4.270379302512826</v>
+        <v>4.194627584955086</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4.455847294724377</v>
+        <v>4.35910234561837</v>
       </c>
     </row>
     <row r="7">
@@ -2505,19 +2505,19 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>3.655824034516262</v>
+        <v>3.631723275826422</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>3.777750701924261</v>
+        <v>3.739677085256099</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3.911868712055091</v>
+        <v>3.858282152217202</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>4.060119639246211</v>
+        <v>3.98923477946775</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>4.224880454174783</v>
+        <v>4.134611664169218</v>
       </c>
     </row>
     <row r="8">
@@ -2527,19 +2527,19 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>3.505094048591718</v>
+        <v>3.482340915379311</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.615453252943709</v>
+        <v>3.579578158867621</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.736350583564485</v>
+        <v>3.685965701463154</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3.869386193392378</v>
+        <v>3.802892962653738</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4.016501472142912</v>
+        <v>3.932045659247812</v>
       </c>
     </row>
     <row r="9">
@@ -2549,19 +2549,19 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>3.366059133168182</v>
+        <v>3.344541830717306</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>3.466296795192872</v>
+        <v>3.432430716445536</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>3.575693042557749</v>
+        <v>3.528222488745105</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>3.695576689904598</v>
+        <v>3.633063773541118</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3.827546678820739</v>
+        <v>3.7483342876271</v>
       </c>
     </row>
     <row r="11">
@@ -2603,19 +2603,19 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>6.123576759895837</v>
+        <v>6.028624527988761</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>4.776653374199568</v>
+        <v>4.707077311789656</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>3.911868712055091</v>
+        <v>3.858282152217202</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3.309509351127527</v>
+        <v>3.266828366776702</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>2.865813477125984</v>
+        <v>2.830272878529148</v>
       </c>
     </row>
     <row r="14">
@@ -2657,19 +2657,19 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>3.527596574685213</v>
+        <v>3.480792142697278</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>3.719732643370151</v>
+        <v>3.669537147457238</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>3.911868712055091</v>
+        <v>3.858282152217202</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>4.104004780740029</v>
+        <v>4.047027156977163</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>4.296140849424967</v>
+        <v>4.235772161737126</v>
       </c>
     </row>
     <row r="17">
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>3.513717901917142</v>
+        <v>3.463611368523343</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>3.728270212983312</v>
+        <v>3.676203948247754</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>3.911868712055091</v>
+        <v>3.858282152217202</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>4.067969792830735</v>
+        <v>4.013245886672549</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4.199774963637052</v>
+        <v>4.144244615613074</v>
       </c>
     </row>
     <row r="20">
@@ -2765,19 +2765,19 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>2.986435726741846</v>
+        <v>2.950013884855211</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>3.449152219398469</v>
+        <v>3.404148018536207</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>3.911868712055091</v>
+        <v>3.858282152217202</v>
       </c>
       <c r="E21" s="7" t="n">
-        <v>4.374585204711712</v>
+        <v>4.312416285898196</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>4.837301697368336</v>
+        <v>4.766550419579194</v>
       </c>
     </row>
     <row r="23">
@@ -2819,19 +2819,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>3.676460009493625</v>
+        <v>3.622873449655737</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>3.794164360774358</v>
+        <v>3.740577800936469</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>3.911868712055091</v>
+        <v>3.858282152217202</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>4.029573063335822</v>
+        <v>3.975986503497934</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>4.147277414616555</v>
+        <v>4.093690854778667</v>
       </c>
     </row>
     <row r="26">
@@ -2873,19 +2873,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>4.273272416773525</v>
+        <v>4.218764367282918</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>4.092570564414308</v>
+        <v>4.03852325975006</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3.911868712055091</v>
+        <v>3.858282152217202</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>3.731166859695873</v>
+        <v>3.678041044684343</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>3.550465007336656</v>
+        <v>3.497799937151485</v>
       </c>
     </row>
     <row r="29">
@@ -2927,19 +2927,19 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>3.911868712055091</v>
+        <v>3.858282152217202</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>3.736350583564485</v>
+        <v>3.685965701463154</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>3.575693042557749</v>
+        <v>3.528222488745105</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3.42808434756411</v>
+        <v>3.3832762120213</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>3.29199609699272</v>
+        <v>3.249628355568755</v>
       </c>
     </row>
   </sheetData>
@@ -3598,14 +3598,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2.746942674345072</v>
+        <v>2.714712230727169</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C68</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>4.683860662745367</v>
+        <v>4.615060282004475</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v/>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.746942674345072</v>
+        <v>2.714712230727169</v>
       </c>
     </row>
     <row r="13">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2.582455973968002</v>
+        <v>2.550225530350099</v>
       </c>
     </row>
     <row r="15">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>2.746942674345072</v>
+        <v>2.714712230727169</v>
       </c>
     </row>
     <row r="7">
@@ -4076,7 +4076,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>4.683860662745367</v>
+        <v>4.615060282004475</v>
       </c>
     </row>
     <row r="8">
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.117266498324851</v>
+        <v>3.078009852680231</v>
       </c>
     </row>
     <row r="9">
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>4.141215393143995</v>
+        <v>4.087628833306107</v>
       </c>
     </row>
     <row r="10">
@@ -4181,7 +4181,7 @@
         </is>
       </c>
       <c r="C16" s="23" t="n">
-        <v>0.04045008173003765</v>
+        <v>0.03868145694459639</v>
       </c>
     </row>
     <row r="18">
@@ -4228,7 +4228,7 @@
         </is>
       </c>
       <c r="C20" s="7" t="n">
-        <v>2.582455973968002</v>
+        <v>2.550225530350099</v>
       </c>
     </row>
     <row r="21">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>3.933415122174865</v>
+        <v>3.87873495907498</v>
       </c>
     </row>
   </sheetData>
@@ -7734,22 +7734,22 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>Terminal NOPAT = FY2030E NOPAT × (1+g)</t>
+          <t>Terminal NOPAT = FY2030E NOPAT</t>
         </is>
       </c>
       <c r="C44" s="19">
-        <f>F14*(1+C43)</f>
+        <f>F14</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>Plus book depreciation and amortisation, grown one year</t>
+          <t>Plus book depreciation and amortisation</t>
         </is>
       </c>
       <c r="C45" s="19">
-        <f>F12*(1+C43)</f>
+        <f>F12</f>
         <v/>
       </c>
     </row>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="C48" s="19">
-        <f>-C42*37849.906247</f>
+        <f>-C42*37107.751223</f>
         <v/>
       </c>
     </row>
@@ -8001,16 +8001,16 @@
         </is>
       </c>
       <c r="C70" s="7" t="n">
-        <v>2.746942674345072</v>
+        <v>2.714712230727169</v>
       </c>
       <c r="D70" s="7" t="n">
-        <v>4.683860662745367</v>
+        <v>4.615060282004475</v>
       </c>
       <c r="E70" s="7" t="n">
-        <v>3.117266498324851</v>
+        <v>3.078009852680231</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>4.141215393143995</v>
+        <v>4.087628833306107</v>
       </c>
     </row>
   </sheetData>

--- a/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
+++ b/engine/modon_study/MODON_Valuation_Model_10082026_public.xlsx
@@ -2092,7 +2092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2330,29 +2330,27 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>CRPS skill vs carry-anchored random walk</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="n">
-        <v>0.04239890936861235</v>
+          <t>Coverage of the 50% band</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="n">
+        <v>0.5882352941176471</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-      <c r="B22" s="37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+          <t>Coverage of the 80% band</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="n">
+        <v>0.9411764705882353</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Coverage of the 80% band (over-covered: bands run wide)</t>
+          <t>Coverage of the 90% band</t>
         </is>
       </c>
       <c r="B23" s="25" t="n">
@@ -2362,20 +2360,10 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Coverage of the 90% band</t>
-        </is>
-      </c>
-      <c r="B24" s="25" t="n">
-        <v>0.9411764705882353</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
           <t>PIT mean (0.5 = centred)</t>
         </is>
       </c>
-      <c r="B25" s="38" t="n">
+      <c r="B24" s="38" t="n">
         <v>0.439185294117647</v>
       </c>
     </row>
